--- a/単元_素顔同盟_私/生徒用ワークシート.xlsx
+++ b/単元_素顔同盟_私/生徒用ワークシート.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="0&quot;組&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;番&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="00555555"/>
@@ -197,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,14 +237,32 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -247,40 +270,37 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,26 +309,26 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -675,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -737,7 +757,7 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>カギカッコに入れられた語などの働きに注意して語感を捉えながら、二つの作品を批判的に読み、それぞれの文章に表れているものの見方や考え方について考えて、「私が私であること」についての自分の考えを批評文にまとめることができる。</t>
+          <t>カギカッコに入れられた語などの働きに注意して語感を捉えながら、自分で選んだ（または自分で立てた）観点から二つの作品を批判的に読み、それぞれの文章に表れているものの見方や考え方について考えて、「私が私であること」についての自分の考えを批評文にまとめることができる。</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -845,7 +865,7 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>■ 授業の流れ（全7時間）</t>
+          <t>■ 二つの道具を使い分ける　―― ここが今回の単元のいちばん大事なところ</t>
         </is>
       </c>
       <c r="B16" s="9" t="n"/>
@@ -854,141 +874,105 @@
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="9" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>時</t>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>「批判の目」4つ</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>学習内容</t>
+          <t>全員共通の「疑い方」</t>
         </is>
       </c>
       <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>あなたがやること</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>単元開き／「素顔同盟」を読む</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="n"/>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>どう読むか。鵜呑みにせず根拠を確かめる方法。クラス全員が同じものを使う</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>「読みの観点」</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>あなたが決める「どこを見るか」</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n"/>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>「批判の目」4つを受け取る。初発の感想を一文で書く</t>
+          <t>作品のどこに目をつけるか。一人ひとりちがっていい。自分で決める</t>
         </is>
       </c>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="11" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>「素顔同盟」を吟味する</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>先生の主張の“擁護の根拠”を先に3つ探す→反論3つ／宿題：「私」を読む</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>「私」の語りを分析する</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>カギカッコ付きの語を全部丸で囲む→【発問①】を書く</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>「私」の結末を吟味する／協議の準備</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>二作比較表→【発問②】を書く→論題を選び提案メモを作る</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>グループ協議①（論題①②③）</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>10分×3ラウンド。自分の回で提案者をつとめる</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>★ 同じ論題に、班の一人ひとりがちがう観点から答える。だから議論がかみ合いながら、何層にもなる。班は観点がばらけるように組みます。</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>■ 授業の流れ（全7時間）</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>時</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>学習内容</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>あなたがやること</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>グループ協議②（論題④⑤⑥）</t>
+          <t>単元開き／「素顔同盟」を読む</t>
         </is>
       </c>
       <c r="C23" s="11" t="n"/>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>10分×3ラウンド。役割を交代しながら</t>
+          <t>「批判の目」4つを受け取る。初発の感想を一文で書く。★自分の観点を仮決めする</t>
         </is>
       </c>
       <c r="E23" s="11" t="n"/>
@@ -997,87 +981,127 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>代表者パネル協議／まとめ</t>
+          <t>「素顔同盟」を吟味する</t>
         </is>
       </c>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>フロア記録→批評文の「主張の一段落」200字を書き切る</t>
+          <t>先生の主張の“擁護の根拠”を先に3つ探す→反論3つ／★自分の観点を確定し、その観点で見えたことを書く／宿題：「私」を読む</t>
         </is>
       </c>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="11" t="n"/>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>■ 協議の進め方　1ラウンド10分の中身</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>「私」の語りを分析する</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>カギカッコ付きの語を全部丸で囲む→【発問①】を書く</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>「私」の結末を吟味する／協議の準備</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>二作比較表→【発問②】を書く→★自分の観点で「私」から見えたことを書く→提案メモを作る</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>0:00〜2:00</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>提案者が提案メモを読む（主張1文＋本文の根拠2か所）</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="n"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>グループ協議①（論題①②③）</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>10分×3ラウンド。自分の回で提案者をつとめる（自分の観点から答える）</t>
+        </is>
+      </c>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="11" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2:00〜8:00</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>検討。提案者以外は全員、質問か反論を1回以上する</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>グループ協議②（論題④⑤⑥）</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>10分×3ラウンド。おわりに★「自分の観点では見えなかったこと」を書く</t>
+        </is>
+      </c>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="11" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>8:00〜10:00</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>提案者が答える。議論の到達点を1文で言う。記録係が書き取る</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>代表者パネル協議／まとめ</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>フロア記録→批評文の「主張の一段落」200字を書き切る</t>
+        </is>
+      </c>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="11" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>■ 常設の3役割　―― 毎ラウンド、時計回りに交代する</t>
+          <t>■ 協議の進め方　1ラウンド10分の中身</t>
         </is>
       </c>
       <c r="B31" s="9" t="n"/>
@@ -1087,15 +1111,15 @@
       <c r="F31" s="9" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>引用チェック係</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="n"/>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>0:00〜2:00</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>「今の意見、本文のどこ？」と必ず1回きく</t>
+          <t>提案者が提案メモを読む（主張1文＋本文の根拠2か所）</t>
         </is>
       </c>
       <c r="D32" s="11" t="n"/>
@@ -1103,15 +1127,15 @@
       <c r="F32" s="11" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>疑い係</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="n"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2:00〜8:00</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>「しかし」「とはいえ」で始まる発言を必ず1回する（賛成でも反対でもよい）</t>
+          <t>検討。提案者以外は全員、質問か反論を1回以上する</t>
         </is>
       </c>
       <c r="D33" s="11" t="n"/>
@@ -1119,15 +1143,15 @@
       <c r="F33" s="11" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>記録係</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n"/>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>8:00〜10:00</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>提案者の主張と、議論の到達点を1行ずつ書く</t>
+          <t>提案者が答える。議論の到達点を1文で言う。記録係が書き取る</t>
         </is>
       </c>
       <c r="D34" s="11" t="n"/>
@@ -1137,7 +1161,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>■ 協議の論題（6本）　―― 自分が提案者になる論題を1つ選ぶ</t>
+          <t>■ 常設の3役割　―― 毎ラウンド、時計回りに交代する</t>
         </is>
       </c>
       <c r="B36" s="9" t="n"/>
@@ -1147,221 +1171,221 @@
       <c r="F36" s="9" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>「素顔同盟」の先生の主張はまちがっているか</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="n"/>
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>引用チェック係</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>「今の意見、本文のどこ？」と必ず1回きく</t>
+        </is>
+      </c>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="11" t="n"/>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>第5時</t>
-        </is>
-      </c>
+      <c r="F37" s="11" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>「僕」は川を上流へ歩いて自由になれるか。「同盟」という題名は何を暗示するか</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="n"/>
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>疑い係</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>「しかし」「とはいえ」で始まる発言を必ず1回する（賛成でも反対でもよい）</t>
+        </is>
+      </c>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="11" t="n"/>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>第5時</t>
-        </is>
-      </c>
+      <c r="F38" s="11" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>「私」の語り手は良い職員か</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="n"/>
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>記録係</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>提案者の主張と、議論の到達点を1行ずつ書く</t>
+        </is>
+      </c>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="11" t="n"/>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>■ 協議の論題（6本）　―― 論題は全員共通。答え方は「自分の観点から」</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>論題は班のみんなで同じものを考える。ちがうのは入口（観点）。自分が提案者になる論題を1つ決めておく。</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>「素顔同盟」の先生の主張はまちがっているか</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>第5時</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>「何の問題もない」への不安の正体は何か。語り手は何に気づいていないか</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>第6時</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>社会の見方として、より怖いのはどちらの作品か</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>第6時</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>⑥</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>「私が私であること」を支えるのは何か（＝批評文の主題）</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>第6時</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>■ 代表者パネル協議（第7時）　12分×2回</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>「僕」は川を上流へ歩いて自由になれるか。「同盟」という題名は何を暗示するか</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>第5時</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>パネル①</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>「私」の語り手は信頼できるか　―― 前半の班から各1名</t>
-        </is>
-      </c>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>「私」の語り手は良い職員か</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="n"/>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>第5時</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>パネル②</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>「私」が「私」であることを支えるのは何か　―― 後半の班から各1名</t>
-        </is>
-      </c>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>「何の問題もない」への不安の正体は何か。語り手は何に気づいていないか</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="n"/>
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-    </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>★ フロアの人も仕事がある：「自分の考えが動いた発言」を1つ、フロア記録シートに書く。これが批評文の条件③の材料になる。</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>■ 班の人数別　ラウンド割り振り調整表</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="n"/>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="9" t="n"/>
-      <c r="E49" s="9" t="n"/>
-      <c r="F49" s="9" t="n"/>
-    </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>6人</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>1人1回、ぴったり</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="11" t="n"/>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>第6時</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>社会の見方として、より怖いのはどちらの作品か</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>第6時</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>「私が私であること」を支えるのは何か（＝批評文の主題）</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>第6時</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>■ 代表者パネル協議（第7時）　12分×2回</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>5人</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>第6時の3ラウンド目（論題⑥）を2名の共同提案にする</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="n"/>
+          <t>パネル①</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>「私」の語り手は信頼できるか　―― 前半の班から各1名</t>
+        </is>
+      </c>
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="11" t="n"/>
       <c r="F51" s="11" t="n"/>
@@ -1369,39 +1393,35 @@
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>4人</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>論題を①③⑤⑥の4本に絞り、余った2ラウンドを「①と③の再検討」「⑥の練り直し」に充てる</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="n"/>
+          <t>パネル②</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>「私」が「私」であることを支えるのは何か　―― 後半の班から各1名</t>
+        </is>
+      </c>
       <c r="D52" s="11" t="n"/>
       <c r="E52" s="11" t="n"/>
       <c r="F52" s="11" t="n"/>
     </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>7人</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>論題②と⑥を各2名の共同提案にする</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="11" t="n"/>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>★ フロアの人も仕事がある：「自分の考えが動いた発言」を1つ、フロア記録シートに書く。これが批評文の条件③の材料になる。</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>■ 「読みの観点」との対応（国語科の系統表につながります）</t>
+          <t>■ 班の人数別　ラウンド割り振り調整表</t>
         </is>
       </c>
       <c r="B55" s="9" t="n"/>
@@ -1411,85 +1431,260 @@
       <c r="F55" s="9" t="n"/>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>中心になる観点：第1層「視点・語り」／第3層「批評・評価」　　めざす深さ：3（自分の考えをもつ）</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="n"/>
-      <c r="C56" s="15" t="n"/>
-      <c r="D56" s="15" t="n"/>
-      <c r="E56" s="15" t="n"/>
-      <c r="F56" s="15" t="n"/>
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>6人</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>1人1回、ぴったり</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="11" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>5人</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>第6時の3ラウンド目（論題⑥）を2名の共同提案にする</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>4人</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>論題を①③⑤⑥の4本に絞り、余った2ラウンドを「①と③の再検討」「⑥の練り直し」に充てる</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>7人</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>論題②と⑥を各2名の共同提案にする</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="11" t="n"/>
+      <c r="F59" s="11" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>■ 「読みの観点」―― 9つの中から選ぶ。なければ自分で立てる</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>必ず入れる観点は「批評・評価」の1つだけ。あとの1〜2個は【自分で決める】。9つの中にぴったりのものがなければ、自分の言葉で新しい観点を立ててよい。「先生が指定した観点」ではなく「自分が選んだ観点」で読むことが、この単元の課題です。</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>第1層</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>登場人物／設定／構成／視点・語り</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>物語の世界をつかむ</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="n"/>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>第2層</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>表現の工夫／題名／主題</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>ことばの工夫を見る</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="n"/>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>第3層</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>批評・評価（★必修）／自分に生かす</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>読みを自分のものにする</t>
+        </is>
+      </c>
+      <c r="F65" s="19" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>自分で観点を立てた例（過去の3年生より）：「笑顔」「名前」「仕事」「制度・ルール」「気づいていない人」――どれも9つの中にはないが、この二作を読むには強い観点になった。</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="n"/>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="20" t="n"/>
+      <c r="E66" s="20" t="n"/>
+      <c r="F66" s="20" t="n"/>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="21" t="inlineStr">
+        <is>
+          <t>めざす深さ：3（自分の考えをもつ）　／　1 見つける → 2 つなげて考える → 3 自分の考えをもつ</t>
+        </is>
+      </c>
+      <c r="B67" s="21" t="n"/>
+      <c r="C67" s="21" t="n"/>
+      <c r="D67" s="21" t="n"/>
+      <c r="E67" s="21" t="n"/>
+      <c r="F67" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="81">
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="A6:F7"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="B59:F59"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A53:F53"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B53:F53"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="A6:F7"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="D26:F26"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="B51:F51"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="組" error="1〜20の半角数字で入力してね" type="whole" operator="between">
@@ -1531,14 +1726,14 @@
       <c r="D1" s="1" t="n"/>
     </row>
     <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>■ 単元目標：カギカッコに入れられた語などの働きに注意して語感を捉えながら、二つの作品を批判的に読み、それぞれの文章に表れているものの見方や考え方について考えて、「私が私であること」についての自分の考えを批評文にまとめることができる。</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>■ 単元目標：カギカッコに入れられた語などの働きに注意して語感を捉えながら、自分で選んだ（または自分で立てた）観点から二つの作品を批判的に読み、それぞれの文章に表れているものの見方や考え方について考えて、「私が私であること」についての自分の考えを批評文にまとめることができる。</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -1551,60 +1746,60 @@
       <c r="D4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>基準</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>選んだカギカッコ付きの語の働きを、語り手の立場（制度を運用する側であること）と結びつけて説明し、自分の経験と対応させて言いかえている。例：「解決」とは相手が満足することであって、問題が解決することではない、と語り手自身が知っている</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>その語が「言葉だけは立派で中身が空である」ことを示していると説明し、自分の経験を挙げている</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>語を挙げるだけ、または経験を挙げるだけで、カギカッコの働きを説明できていない</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -1617,98 +1812,98 @@
       <c r="D10" s="7" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>★★ B と A の分かれ目 ★★　　条件①（両作品からの引用）と条件②（「しかし／とはいえ」の疑いの一文）の【両方】に触れていなければ、A以上にはならない。</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>★★ B と A の分かれ目 ★★　　条件①（自分の観点を示し、その観点から両作品を引用）と条件②（「しかし／とはいえ」の疑いの一文）の【両方】に触れていなければ、A以上にはならない。</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>基準</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>条件①②を満たし、さらに協議で自分の考えが動いた地点を示して自分の生活・社会と結んでいる。加えて、自分の評価の前提や限界にも触れている（例：私は最初、僕に共感していた。しかしそれは、僕が私たちと同じ側にいるように書かれていたからだ）</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>条件①②を満たし、さらに協議で自分の考えが動いた地点を示して自分の生活・社会と結んでいる。加えて、【自分の観点だから見えたこと／その観点では見えなかったこと】の両方に触れ、自分の読みの前提や限界を自分で述べている（例：私は「笑顔」という観点で読んだので、仮面を外す場面ばかり見ていた。班の人の「制度」という観点を聞いて、僕が向かう森も一つの制度かもしれないと気づいた）</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>条件①②の【両方】を満たしている。両作品から引用し、それぞれの見方のちがいを捉え、少なくとも一方の見方に「しかし／とはいえ」で疑いを差しはさんでいる</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>条件①②の【両方】を満たしている。自分の観点を示し、その観点から両作品を引用してそれぞれの見方のちがいを捉え、少なくとも一方の見方に「しかし／とはいえ」で疑いを差しはさんでいる</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>条件①②の【どちらか一方のみ】。両作品を引用しているが疑いがない、または疑いはあるが引用が一方の作品にしかない</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>条件①②の【どちらか一方のみ】。観点を示して引用しているが疑いがない、または疑いはあるが観点が示されていない／引用が一方の作品にしかない</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>両作品に触れているが、引用も疑いもなく、あらすじや感想が中心</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>両作品に触れているが、観点も引用も疑いもなく、あらすじや感想が中心</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>一方の作品にしか触れていない、または未完</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -1721,60 +1916,60 @@
       <c r="D19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>基準</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>提案者として本文の根拠を示して自分の読みを述べ、他者の異なる読みを受けて自分の考えを述べ直している</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>自分で観点を選び（または立て）、その観点から本文の根拠を示して提案し、他の観点からの指摘を受けて自分の読みを述べ直している（「自分の観点では見えなかったこと」の欄に、他者から得たものが具体的に書かれている）</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>提案者の役割を果たし、他のラウンドでも質問か反論を述べている</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>自分で観点を決め、提案者の役割を果たし、他のラウンドでも質問か反論を述べている</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>提案メモが未記入、または協議で発言していない</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>観点が未記入、提案メモが未記入、または協議で発言していない</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1829,14 +2024,14 @@
       <c r="D1" s="1" t="n"/>
     </row>
     <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>■ 単元目標：カギカッコに入れられた語などの働きに注意して語感を捉えながら、二つの作品を批判的に読み、それぞれの文章に表れているものの見方や考え方について考えて、「私が私であること」についての自分の考えを批評文にまとめることができる。</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>■ 単元目標：カギカッコに入れられた語などの働きに注意して語感を捉えながら、自分で選んだ（または自分で立てた）観点から二つの作品を批判的に読み、それぞれの文章に表れているものの見方や考え方について考えて、「私が私であること」についての自分の考えを批評文にまとめることができる。</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -1849,74 +2044,74 @@
       <c r="D4" s="9" t="n"/>
     </row>
     <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>【発問①／知識・技能】　150〜200字
 「私」の語り手は、「解決」「誠意」「対応」「模範的」「正常な状態」のように、大事な言葉をわざわざカギカッコに入れて使う。この中から一つ選び、あなた自身が「言葉だけは立派なのに中身がない」と感じた経験を一つ挙げたうえで、語り手がその言葉をカギカッコに入れて使うのはなぜか、自分の言葉で説明しよう。</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
     </row>
     <row r="6" ht="108" customHeight="1">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="14">
+      <c r="A6" s="27" t="n"/>
+      <c r="B6" s="27" t="n"/>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="17">
         <f>IF(A6="","0/200字",LEN(A6)&amp;"/200字")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>🤖 まず自分の経験と考えを自分の言葉で書こう。書き終わったら「AIプロンプト」シートの【壁打ち①】を使って、考えを深めるヒントをもらう。AIに答えを書いてもらうのではなく、フィードバックをもらうのが目的だよ。</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>【発問②／思考・判断・表現】　200〜250字
 「素顔同盟」の先生は「仮面は私たちに真の平和と自由を与えてくれた」と言う。もし明日からあなたのクラス全員が仮面をつけることになったら、何が良くなり、何が失われるだろうか。そのうえで、先生の主張と「僕」の見方の、どちらがより危ないと思うか、本文の言葉を引いて書こう。</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
     </row>
     <row r="10" ht="126" customHeight="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="14">
+      <c r="A10" s="27" t="n"/>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="17">
         <f>IF(A10="","0/250字",LEN(A10)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="39" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>🤖 「僕が正しい」で終わっていないか自分で点検しよう。仮面のおかげで避けられている争いは、本文に書かれていないかな。自分の考えを書いたあとで【壁打ち①】に①②まとめて見せるとよい。AIに判断してもらうのではなく、見落としを教えてもらうつもりで。</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>■ まとめ活動　批評文（800字）　第7時＋家庭学習</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -1928,121 +2123,121 @@
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>【課題】二つの作品は、「私が私であること」を何が支え、何が奪うと考えているか。二つの作品のものの見方・考え方を検討したうえで、あなた自身の考えを書きなさい。（800字）</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-    </row>
-    <row r="16" ht="62" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>【課題】あなたが選んだ観点から読むと、二つの作品は「私が私であること」を何が支え、何が奪うと考えているか。二つの作品のものの見方・考え方を検討したうえで、あなた自身の考えを書きなさい。（800字）</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+    </row>
+    <row r="16" ht="78" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>【必ず入れること】
-① 両作品からそれぞれ一か所以上引用し、その作品が「私が私であること」について何を支え・何が奪うと考えているかを示す
+① 自分が選んだ（立てた）観点を最初に示し、その観点から両作品をそれぞれ一か所以上引用して、その作品が「私が私であること」について何を支え・何が奪うと考えているかを示す
 ② 少なくとも一方の作品の見方に対して、「しかし」「とはいえ」で始まる疑いの一文を入れる
-③ 代表者協議で自分の考えが動いた発言に触れ、自分の生活や今の社会と結ぶ</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
+③ 協議で自分の考えが動いた発言に触れ、「自分の観点では見えなかったこと」を書き、自分の生活や今の社会と結ぶ</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>★ ①と②の両方に触れていないと、A以上にはならないよ。③まで書けるとSに届く。</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n"/>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>【構想メモ】　主張1文／「素顔同盟」からの引用／「私」からの引用／考えが動いた発言</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>【構想メモ】　自分の観点／主張1文／「素顔同盟」からの引用／「私」からの引用／考えが動いた発言／自分の観点では見えなかったこと</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
     </row>
     <row r="19" ht="96" customHeight="1">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="27" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>🤖 構想メモが書けたら「AIプロンプト」シートの【壁打ち②】で、条件①②を満たしているかだけ確認してもらおう。AIに構想を作ってもらうのはNG。自分の構想を点検してもらうために使う。</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>【第7時に教室で書く：主張の一段落（200字）】　主張1文＋「素顔同盟」からの引用＋「私」からの引用をつなげる</t>
-        </is>
-      </c>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>【第7時に教室で書く：主張の一段落（200字）】　「私は○○という観点で読んだ」＋主張1文＋「素顔同盟」からの引用＋「私」からの引用をつなげる</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="32" t="n"/>
     </row>
     <row r="23" ht="84" customHeight="1">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="14">
+      <c r="A23" s="27" t="n"/>
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="17">
         <f>IF(A23="","0/200字",LEN(A23)&amp;"/200字")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>【批評文（800字）】　上の一段落を核にして、家庭学習で800字に展開する　★提出するのはここ</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n"/>
-      <c r="C24" s="28" t="n"/>
-      <c r="D24" s="28" t="n"/>
+      <c r="B24" s="33" t="n"/>
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
     </row>
     <row r="25" ht="300" customHeight="1">
-      <c r="A25" s="22" t="n"/>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="29">
+      <c r="A25" s="27" t="n"/>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="34">
         <f>IF(A25="","0/800字",LEN(A25)&amp;"/800字")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>🤖 書き終わったら「AIプロンプト」シートの【添削】を使って、条件①②③のチェックとヒントだけもらおう。AIに書き直してもらってはいけない。直すのは自分の手で。</t>
         </is>
       </c>
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="23" t="n"/>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>■ AIの評価と、自分の評価</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="30" t="n"/>
+      <c r="B28" s="35" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="35" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
@@ -2051,8 +2246,8 @@
         </is>
       </c>
       <c r="B29" s="10" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
@@ -2061,8 +2256,8 @@
         </is>
       </c>
       <c r="B30" s="10" t="n"/>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
+      <c r="C30" s="37" t="n"/>
+      <c r="D30" s="37" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
@@ -2071,63 +2266,63 @@
         </is>
       </c>
       <c r="B31" s="10" t="n"/>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="33" t="n"/>
+      <c r="C31" s="38" t="n"/>
+      <c r="D31" s="38" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>🤖 AIの評価と自分の評価がずれたときが、いちばん学べるところ。どちらが正しいかではなく、なぜずれたのかを考えよう。</t>
         </is>
       </c>
-      <c r="B32" s="23" t="n"/>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23" t="n"/>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>【評価のちがいを考える】　AIの評価と自分の評価はなぜずれた（または一致した）のか（100字くらい）</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
+      <c r="B33" s="32" t="n"/>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="32" t="n"/>
     </row>
     <row r="34" ht="72" customHeight="1">
-      <c r="A34" s="22" t="n"/>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="14">
+      <c r="A34" s="27" t="n"/>
+      <c r="B34" s="27" t="n"/>
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="17">
         <f>IF(A34="","0/100字",LEN(A34)&amp;"/100字")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>■ ふりかえり</t>
         </is>
       </c>
-      <c r="B36" s="34" t="n"/>
-      <c r="C36" s="34" t="n"/>
-      <c r="D36" s="34" t="n"/>
+      <c r="B36" s="39" t="n"/>
+      <c r="C36" s="39" t="n"/>
+      <c r="D36" s="39" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>【ふりかえり】　この単元で、自分の読み方はどこが変わったか。「批判の目」の①〜④のどれがいちばん役に立ったか（150字くらい）</t>
         </is>
       </c>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
+      <c r="B37" s="32" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="32" t="n"/>
     </row>
     <row r="38" ht="96" customHeight="1">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="14">
+      <c r="A38" s="27" t="n"/>
+      <c r="B38" s="27" t="n"/>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="17">
         <f>IF(A38="","0/150字",LEN(A38)&amp;"/150字")</f>
         <v/>
       </c>
@@ -2199,7 +2394,7 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>共通ルール：自分の名前は書かない／まず自分で書いてから使う／AIに書いてもらうのではなく、フィードバックをもらう</t>
         </is>
@@ -2213,7 +2408,7 @@
       </c>
     </row>
     <row r="5" ht="330" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>あなたは中学校国語の先生です。中学3年生にわかりやすい言葉で答えてください。
 私は「素顔同盟」（すやまたけし）と「私」（三崎亜記）という二つの小説を、批判的に読む学習をしています。
@@ -2241,7 +2436,7 @@
       </c>
     </row>
     <row r="8" ht="400" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>あなたは中学校国語の先生です。中学3年生にわかりやすい言葉で答えてください。
 私は「素顔同盟」（すやまたけし）と「私」（三崎亜記）について、批評文（800字）を書きます。
@@ -2249,12 +2444,15 @@
 【課題】二つの作品は、「私が私であること」を何が支え、何が奪うと考えているか。
 二つの作品のものの見方・考え方を検討したうえで、自分の考えを書く。
 【必ず入れる条件】
-① 両作品からそれぞれ一か所以上引用し、その作品が「私が私であること」について
-   何を支え・何が奪うと考えているかを示す
+① 自分が選んだ（自分で立てた）観点を最初に示し、その観点から両作品をそれぞれ一か所以上
+   引用して、その作品が「私が私であること」について何を支え・何が奪うと考えているかを示す
 ② 少なくとも一方の作品の見方に対して、「しかし」「とはいえ」で始まる疑いの一文を入れる
-③ 話し合いで自分の考えが動いた発言に触れ、自分の生活や今の社会と結ぶ
+③ 話し合いで自分の考えが動いた発言に触れ、「自分の観点では見えなかったこと」を書き、
+   自分の生活や今の社会と結ぶ
 下に私の構想メモを貼ります。①②③を満たしているかをチェックして、
 足りないところを教えてください。読んでいない友達に伝わるかも見てください。
+★私の観点そのものを「別の観点にしたほうがよい」と言い換えないでください。
+　私が選んだ観点のまま、その観点で読みを深めるための助言をください。
 ★注意：構想を代わりに作らないでください。私の構想への助言だけをください。300字以内で。
 ――――――――――――――――
 【私の構想メモ】
@@ -2271,17 +2469,19 @@
       </c>
     </row>
     <row r="11" ht="360" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>あなたは中学校国語の先生です。中学3年生にわかりやすい言葉で答えてください。
 下に私が書いた批評文（800字）を貼ります。読む相手は、まだ「素顔同盟」も「私」も
 読んでいない隣のクラスの友達です。
 次のチェックリストで確認し、ヒントをください。
-□ ① 両作品からそれぞれ一か所以上引用しているか。その引用が根拠になっているか
+□ ① 自分の観点が最初に示されているか。その観点から両作品を引用し、引用が根拠になっているか
 □ ② 少なくとも一方の作品の見方に「しかし」「とはいえ」で疑いを差しはさんでいるか
-□ ③ 話し合いで考えが動いた発言に触れ、自分の生活や社会と結んでいるか
+□ ③ 話し合いで考えが動いた発言に触れ、「自分の観点では見えなかったこと」を書き、
+     自分の生活や社会と結んでいるか
 □ 読んでいない友達にも、二つの作品の中身が伝わるか
 □ あらすじの説明が長すぎて、自分の考えが薄くなっていないか
+★私の観点を別の観点に置きかえる提案はしないでください。この観点のままで深める助言をください。
 ★注意：書き直した文章を出さないでください。直すのは私です。ヒントだけを400字以内で。
 ――――――――――――――――
 【私の批評文】
@@ -2301,7 +2501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2321,325 +2521,479 @@
       <c r="D1" s="1" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>■ 二作比較表（第4時）　―― 批評文の材料になる。ここを埋めれば書ける</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>■ ① 自分の読みの観点を決める（第1時のおわり〜第2時）　★この単元の出発点</t>
+        </is>
+      </c>
+      <c r="B3" s="41" t="n"/>
+      <c r="C3" s="41" t="n"/>
+      <c r="D3" s="41" t="n"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>「批評・評価」は全員必修。あとの1〜2個は自分で決める。9つの中にぴったりのものがなければ、自分の言葉で新しい観点を立ててよい。（9つ＝登場人物／設定／構成／視点・語り／表現の工夫／題名／主題／批評・評価／自分に生かす）</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>私が選んだ観点（1〜2個）　または自分で立てた観点の名前</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>その観点を選んだ理由　――　この二作のどこが気になったからか</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n"/>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="27" t="n"/>
+    </row>
+    <row r="7" ht="66" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>【第2時】その観点で「素顔同盟」から見えたこと（本文のことばを入れて）</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>【第4時】その観点で「私」から見えたこと（本文のことばを入れて）</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>★ 観点は第2時のおわりに先生が見ます。班は「観点がばらけるように」組みます。同じ論題に、一人ひとりちがう入口から答えるためです。</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>■ ② 二作比較表（第4時）　―― 批評文の材料になる。ここを埋めれば書ける</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>比べること</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>素顔同盟</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>私</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>気づいたこと</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>「私」を消すものは何か</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>語り手はどんな立場の人か</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>語り手は自分の状況に気づいているか</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>結末で語り手は何をするか</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>読者は語り手に共感できるか</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>この作品は何を良いこととして書いているか</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="B18" s="27" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>本文の根拠（引用したい一文）</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>■ 提案メモ（第4時に作る／第5・6時で読む）　―― これを2分で読んで議論を始める</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>■ ③ 提案メモ（第4時に作る／第5・6時で読む）　―― これを2分で読んで議論を始める</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>★ 論題は班で共通。あなたは「自分の観点から」その論題に答える。だから同じ論題でも、班の人と言うことがちがってよい（ちがうほうがよい）。</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>自分が提案者になる論題の番号（①〜⑥）</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="36" t="n"/>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>主張（1文で言い切る）</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="42" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>私の観点（上で決めたもの）</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>主張（1文で言い切る）　――「◯◯という観点から見ると、…」の形で</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>根拠となる本文①（引用＋何ページ何行目か）</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="B26" s="27" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>根拠となる本文②（引用＋何ページ何行目か）</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="B27" s="27" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>反対されそうなこと、と自分の答え</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>■ 記録係シート（第5・6時）　―― 自分が記録係のラウンドで書く</t>
-        </is>
-      </c>
-      <c r="B20" s="37" t="n"/>
-      <c r="C20" s="37" t="n"/>
-      <c r="D20" s="37" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="B28" s="27" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>■ ④ 記録係シート（第5・6時）　―― 自分が記録係のラウンドで書く</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="n"/>
+      <c r="C30" s="41" t="n"/>
+      <c r="D30" s="41" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>ラウンド</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>提案者の主張（1行）</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>議論の到達点（1行）</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>論題</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>提案者の観点</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>第1 ラウンド</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B32" s="27" t="n"/>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="27" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>第2 ラウンド</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="B33" s="27" t="n"/>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="27" t="n"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>第3 ラウンド</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="B34" s="27" t="n"/>
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="27" t="n"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>第4 ラウンド</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="B35" s="27" t="n"/>
+      <c r="C35" s="27" t="n"/>
+      <c r="D35" s="27" t="n"/>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>第5 ラウンド</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="B36" s="27" t="n"/>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>第6 ラウンド</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="34" t="inlineStr">
-        <is>
-          <t>■ フロア記録シート（第7時）　―― パネルを聞きながら書く。批評文の条件③の材料</t>
-        </is>
-      </c>
-      <c r="B29" s="34" t="n"/>
-      <c r="C29" s="34" t="n"/>
-      <c r="D29" s="34" t="n"/>
-    </row>
-    <row r="30" ht="54" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>パネル①で「自分の考えが動いた発言」（だれの、どんな発言か）</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-    </row>
-    <row r="31" ht="54" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="41" t="inlineStr">
+        <is>
+          <t>■ ⑤ 第6時のおわりに：自分の観点では見えなかったこと　★批評文の条件③の中心</t>
+        </is>
+      </c>
+      <c r="B39" s="41" t="n"/>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="41" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>6ラウンドを終えて書く。ここが書けると、自分の読みを自分で吟味したことになる。</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>私の観点だから見えたこと（ほかの人は言わなかったこと）</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="n"/>
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="27" t="n"/>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>私の観点では見えなかったこと（だれの、どの観点から教わったか）</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="n"/>
+      <c r="C42" s="27" t="n"/>
+      <c r="D42" s="27" t="n"/>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>それを知って、自分の読みはどう変わったか</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n"/>
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="27" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>■ ⑥ フロア記録シート（第7時）　―― パネルを聞きながら書く</t>
+        </is>
+      </c>
+      <c r="B45" s="39" t="n"/>
+      <c r="C45" s="39" t="n"/>
+      <c r="D45" s="39" t="n"/>
+    </row>
+    <row r="46" ht="54" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>パネル①で「自分の考えが動いた発言」（だれの、どんな観点からの発言か）</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="n"/>
+      <c r="C46" s="27" t="n"/>
+      <c r="D46" s="27" t="n"/>
+    </row>
+    <row r="47" ht="54" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">　なぜ動いたのか（自分はそれまでどう考えていたか）</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-    </row>
-    <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="B47" s="27" t="n"/>
+      <c r="C47" s="27" t="n"/>
+      <c r="D47" s="27" t="n"/>
+    </row>
+    <row r="48" ht="54" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>パネル②で「自分の考えが動いた発言」</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-    </row>
-    <row r="33" ht="54" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="B48" s="27" t="n"/>
+      <c r="C48" s="27" t="n"/>
+      <c r="D48" s="27" t="n"/>
+    </row>
+    <row r="49" ht="54" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">　なぜ動いたのか</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
+      <c r="B49" s="27" t="n"/>
+      <c r="C49" s="27" t="n"/>
+      <c r="D49" s="27" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B33:D33"/>
+  <mergeCells count="28">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/単元_素顔同盟_私/生徒用ワークシート.xlsx
+++ b/単元_素顔同盟_私/生徒用ワークシート.xlsx
@@ -824,10 +824,10 @@
       <c r="E15" s="12" t="n"/>
       <c r="F15" s="12" t="n"/>
     </row>
-    <row r="16" ht="24" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>必修は「批評・評価」だけ。あと1〜2個は自分で決める。9つになければ、自分で新しい観点を作ってよい。</t>
+          <t>必修は「批評・評価」だけ。あと1〜2個を、下の8つから自分で選ぶ。</t>
         </is>
       </c>
       <c r="B16" s="13" t="n"/>
@@ -887,7 +887,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>自分で作った観点の例：「笑顔」「名前」「仕事」「制度」「気づかない人」</t>
+          <t>めざす深さ：3（自分の考えをもつ）　1 見つける → 2 つなげて考える → 3 自分の考えをもつ</t>
         </is>
       </c>
       <c r="B20" s="14" t="n"/>
@@ -1478,7 +1478,7 @@
       <c r="C12" s="17" t="n"/>
       <c r="D12" s="17" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>S</t>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>①②に加え、自分の観点では見えなかったことに触れ、今の考えを述べている</t>
+          <t>①②に加え、自分の観点では見えなかったことに触れ、今の考えを述べている（例：「表現の工夫」で読んだので笑顔の描き方ばかり見ていた。「題名」の観点を聞いて、選べるかどうかを見ていなかったと気づいた）</t>
         </is>
       </c>
       <c r="C13" s="11" t="n"/>
@@ -2160,10 +2160,10 @@
       <c r="C3" s="12" t="n"/>
       <c r="D3" s="12" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>必修は「批評・評価」だけ。あと1〜2個は自分で決める。9つになければ自分で作る。</t>
+          <t>必修は「批評・評価」。あと1〜2個を9つから選ぶ。（登場人物／設定／構成／視点・語り／表現の工夫／題名／主題／自分に生かす）</t>
         </is>
       </c>
       <c r="B4" s="13" t="n"/>
@@ -2173,7 +2173,7 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>私の観点（1〜2個）</t>
+          <t>私の観点（9つから1〜2個）</t>
         </is>
       </c>
       <c r="B5" s="22" t="n"/>

--- a/単元_素顔同盟_私/生徒用ワークシート.xlsx
+++ b/単元_素顔同盟_私/生徒用ワークシート.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="単元ガイド" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="評価基準" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="発問・回答" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="考えをまとめる" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="AIプロンプト" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="話し合いワーク" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -65,6 +65,10 @@
       <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="00555555"/>
       <sz val="9"/>
     </font>
@@ -84,17 +88,12 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="001A5276"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="11"/>
+      <color rgb="001A5276"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Consolas"/>
@@ -226,71 +225,71 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -657,11 +656,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -719,7 +718,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>カギカッコに入れた語などの働きに注意して語感を捉えながら、自分で決めた観点から二つの作品を批判的に読み、文章に表れたものの見方や考え方について、根拠を示してグループで話し合うことができる。</t>
+          <t>自分で決めた観点と「批評・評価」の観点から二つの作品を批判的に読み、三つの論題について文章に表れたものの見方や考え方を捉えて、根拠を示してグループで話し合うことができる。</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -827,7 +826,7 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>必修は「批評・評価」だけ。あと1〜2個を、下の8つから自分で選ぶ。</t>
+          <t>必修は「批評・評価」だけ。あと1〜2個を、下の「批評・評価」以外の8つから自分で選ぶ。（複数も可）</t>
         </is>
       </c>
       <c r="B16" s="13" t="n"/>
@@ -836,15 +835,16 @@
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>第1層</t>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>第1層
+何が描かれているか</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>登場人物／設定／構成／視点・語り</t>
+          <t>登場人物　　設定　　構成　　視点・語り</t>
         </is>
       </c>
       <c r="C17" s="11" t="n"/>
@@ -852,15 +852,16 @@
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="11" t="n"/>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>第2層</t>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>第2層
+どう描かれているか</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>表現の工夫／題名／主題</t>
+          <t>表現の工夫　　題名　　主題</t>
         </is>
       </c>
       <c r="C18" s="11" t="n"/>
@@ -868,33 +869,22 @@
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="11" t="n"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>第3層</t>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>第3層
+自分はどう考えるか</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>批評・評価（必修）／自分に生かす</t>
+          <t>批評・評価（必修）　　自分に生かす</t>
         </is>
       </c>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>めざす深さ：3（自分の考えをもつ）　1 見つける → 2 つなげて考える → 3 自分の考えをもつ</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
@@ -911,7 +901,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>■ 授業の流れ（全7時間）</t>
+          <t>■ 話し合いの論題（3つ）　―― 3つとも、二つの作品にまたがる問い</t>
         </is>
       </c>
       <c r="B23" s="9" t="n"/>
@@ -921,138 +911,142 @@
       <c r="F23" s="9" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>★ 当日、どの論題で発表するか知らされる。3つすべて準備しておく。</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>論題1</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>仮面とデータは、同じものか</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>二つの作品で「私」を消しているもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>論題2</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>気づいている「僕」と、気づいていない「私」。どちらが危ういか</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>二つの語り手</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>論題3</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>二つの作品は、「私」を支えるものを示せているか</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>二つの結末</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>5時＝1周目（出し合う）／6時＝2周目（別の観点をふまえて問い直す）</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>■ 授業の流れ（全7時間）</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>1時</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>「素顔同盟」を読む／批判の目を知る／観点を仮決め</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>「素顔同盟」「私」を読む／批判の目を知る／観点を仮決め</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>2時</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>先生の主張を吟味／観点を決める／観点で見えたことを書く</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>3時</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>「私」の語りを読む／発問①</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>4時</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>「私」の結末を読む／比較表／発問②／提案メモ</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>5時</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>話し合い1周目（論題1→2→3）</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>6時</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>話し合い2周目（論題1→2→3）／見えなかったことを書く</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>7時</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>まとめのディスカッション／300字を書く</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>■ 話し合いの論題（3つ）</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>「素顔同盟」を吟味／観点を決める／論題1の考えをまとめる</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>論題1</t>
+          <t>3時</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>仮面を捨てた先に、自由はあるか　（素顔同盟）</t>
+          <t>「私」の語りと結末を吟味／論題2の考えをまとめる</t>
         </is>
       </c>
       <c r="C33" s="11" t="n"/>
@@ -1063,12 +1057,12 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>論題2</t>
+          <t>4時</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>「何の問題もない」と言う語り手は、何に気づいていないか　（私）</t>
+          <t>二作比較表／論題3の考えをまとめる／3つを見直す</t>
         </is>
       </c>
       <c r="C34" s="11" t="n"/>
@@ -1079,12 +1073,12 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>論題3</t>
+          <t>5時</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>「私」が「私」であることを支えるのは何か　（両方）</t>
+          <t>話し合い1周目　★はじめに発表する人と論題が知らされる</t>
         </is>
       </c>
       <c r="C35" s="11" t="n"/>
@@ -1092,56 +1086,60 @@
       <c r="E35" s="11" t="n"/>
       <c r="F35" s="11" t="n"/>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>5時＝1周目（出し合う）／6時＝2周目（別の観点をふまえて問い直す）</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>■ 1ラウンド10分の中身　／　役割は毎回交代</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>0〜2分</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>提案者が読む（観点＋主張＋本文の根拠2つ）</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>6時</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>話し合い2周目　／　考えが動いたところを書く</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>7時</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>まとめのディスカッション／見直しを仕上げる</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>■ 7時：まとめのディスカッション</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>2〜8分</t>
+          <t>パネル①（12分）</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>検討。ほかの人は全員、質問か反論を1回以上</t>
+          <t>仮面とデータは、同じものか</t>
         </is>
       </c>
       <c r="D40" s="11" t="n"/>
@@ -1151,13 +1149,13 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>8〜10分</t>
+          <t>パネル②（12分）</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>提案者が答える。到達点を1文にする</t>
+          <t>二つの作品は、「私」を支えるものを示せているか</t>
         </is>
       </c>
       <c r="D41" s="11" t="n"/>
@@ -1165,168 +1163,63 @@
       <c r="F41" s="11" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>引用チェック係</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="n"/>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>聞く人の仕事</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>「本文のどこ？」を必ず1回きく</t>
+          <t>考えが動いた発言を1つ記録する</t>
         </is>
       </c>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="11" t="n"/>
       <c r="F42" s="11" t="n"/>
     </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>疑い係</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="n"/>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>「しかし」「とはいえ」で始める発言を必ず1回</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>記録係</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>主張と到達点を1行ずつ書く</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>■ 7時：まとめのディスカッション</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>パネル①（12分）</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>二つの作品は、何が「私」を消すと言っているか</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>パネル②（12分）</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>「私」が「私」であることを支えるのは何か</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="11" t="n"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>聞く人の仕事</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>考えが動いた発言を1つ記録する</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="41">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="C39:F39"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="B31:F31"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B27:F27"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="B26:E26"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="A40:B40"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A6:F7"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B28:F28"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A47:B47"/>
     <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C47:F47"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="C40:F40"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A43:B43"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C43:F43"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A44:B44"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
   <dataValidations count="2">
@@ -1349,7 +1242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1371,282 +1264,233 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>目標：カギカッコに入れた語などの働きに注意して語感を捉えながら、自分で決めた観点から二つの作品を批判的に読み、文章に表れたものの見方や考え方について、根拠を示してグループで話し合うことができる。</t>
+          <t>目標：自分で決めた観点と「批評・評価」の観点から二つの作品を批判的に読み、三つの論題について文章に表れたものの見方や考え方を捉えて、根拠を示してグループで話し合うことができる。</t>
         </is>
       </c>
       <c r="B2" s="8" t="n"/>
       <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>【知識・技能】語感　／　見るもの：発問①</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>この単元で評価するのは【思考・判断・表現】と【主体的に学習に取り組む態度】の2つ。</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>【思考・判断・表現】批判的に読む　／　見るもの：まとめた3つの記述　＋　当日の発言</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>★ AとBの分かれ目 ★　条件①（3つの論題すべてを、観点と本文の根拠でまとめた）と条件②（当日、自分の観点から根拠を示して発言した）の【両方】が必要</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>基準</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>カギカッコの語の働きを、語り手の立場と結びつけて説明している</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>その語が「言葉だけ立派で中身が空」と示すことを説明し、自分の経験を挙げている</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>語を挙げるだけ、または経験を挙げるだけ</t>
+          <t>①②に加え、他の観点を受けて考えを見直し、自分の観点では見えなかったことに触れて今の考えを述べている</t>
         </is>
       </c>
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="11" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>【思考・判断・表現】批判的に読む　／　見るもの：7時の300字</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>★ AとBの分かれ目 ★　条件①（観点＋本文の根拠で主張した）と条件②（他の観点を受けて考えを見直した）の【両方】が必要</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>①②の両方。3つの論題すべてを観点と本文の根拠でまとめ、当日も自分の観点から根拠を示して発言した</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>①②の一方だけ。準備はあるが発言が根拠に届かない、または発言はよいが3つそろっていない</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>準備が1〜2論題だけで本文の根拠がない、または発言していない</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>準備がほとんどない</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>※ どの観点を選んだかでは評価しない。どの観点でも、根拠を示して吟味できていればよい。</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>※ AIの評価は「まとめた記述」だけを見た暫定。当日の発言は先生が加えて確定する。</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>【主体的に学習に取り組む態度】　／　見るもの：観点・3つの準備・話し合い</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>基準</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>①②に加え、自分の観点では見えなかったことに触れ、今の考えを述べている（例：「表現の工夫」で読んだので笑顔の描き方ばかり見ていた。「題名」の観点を聞いて、選べるかどうかを見ていなかったと気づいた）</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>①②の両方。観点と本文の根拠で主張し、他の観点を受けて考えを見直している</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>自分で観点を決め、3つの論題すべてを準備し、他の観点を受けて読みを述べ直した</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>①②の一方だけ。主張はあるが見直しがない、または見直しに根拠がない</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>自分で観点を決め、3つの論題を準備し、提案者をつとめ、ほかの回でも質問か反論をした</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>話し合いの感想だけ。主張も見直しもない</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>記述が乏しい、または一方の作品にしか触れていない</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>※ 観点の種類では評価しない。どんな観点でも、根拠を示して吟味できていればよい。</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>【主体的に学習に取り組む態度】　／　見るもの：観点・提案メモ・話し合い</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>段階</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>基準</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>自分で観点を決め、根拠を示して提案し、他の観点を受けて読みを述べ直した</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>自分で観点を決め、提案者をつとめ、ほかの回でも質問か反論をした</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>観点や提案メモが未記入、または発言していない</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>観点や準備が未記入、または発言していない</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A4:D4"/>
+  <mergeCells count="18">
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1658,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1670,7 +1514,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>発問・回答</t>
+          <t>考えをまとめる</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1680,7 +1524,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>目標：カギカッコに入れた語などの働きに注意して語感を捉えながら、自分で決めた観点から二つの作品を批判的に読み、文章に表れたものの見方や考え方について、根拠を示してグループで話し合うことができる。</t>
+          <t>目標：自分で決めた観点と「批評・評価」の観点から二つの作品を批判的に読み、三つの論題について文章に表れたものの見方や考え方を捉えて、根拠を示してグループで話し合うことができる。</t>
         </is>
       </c>
       <c r="B2" s="8" t="n"/>
@@ -1690,333 +1534,283 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>■ 発問（3時・4時）</t>
+          <t>■ 3つの論題について、考えをまとめる（2時〜4時）</t>
         </is>
       </c>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="9" t="n"/>
       <c r="D4" s="9" t="n"/>
     </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>【発問①】150〜200字
-「私」の語り手は「解決」「誠意」「模範的」「正常な状態」をカギカッコに入れて使う。1つ選び、あなたが「言葉だけ立派で中身がない」と感じた経験を挙げて、なぜカギカッコに入れるのか書こう。</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-    </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="23">
-        <f>IF(A6="","0/200字",LEN(A6)&amp;"/200字")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>★ 当日、どの論題で発表するか知らされる。だから3つすべて準備しておく。</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>私の観点：批評・評価（必修）＋</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>🤖 まず自分で書く。書いたら【壁打ち①】へ。AIに書かせず、ヒントをもらう。</t>
+          <t>【3つとも同じ3点を書く】① 批評・評価として、どう評価するか（主張1文）　② 自分の観点から見えたこと　③ 本文の根拠（引用）</t>
         </is>
       </c>
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="24" t="n"/>
       <c r="D7" s="24" t="n"/>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>【発問②】200〜250字
-「素顔同盟」の先生は「仮面は真の平和と自由を与えた」と言う。もし明日クラス全員が仮面をつけたら、何が良くなり何が失われるか。そのうえで、先生と「僕」のどちらがより危ないか、本文を引いて書こう。</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-    </row>
-    <row r="10" ht="118" customHeight="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="23">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>【論題1】仮面とデータは、同じものか　―― 二つの作品で「私」を消しているもの</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="25" t="n"/>
+      <c r="D9" s="25" t="n"/>
+    </row>
+    <row r="10" ht="140" customHeight="1">
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="16">
         <f>IF(A10="","0/250字",LEN(A10)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>🤖 「僕が正しい」で終わっていないか。仮面の利点も本文にある。→【壁打ち①】</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>■ まとめ　＝　ディスカッション（5時→7時）</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>この単元のまとめは話し合いそのもの。下の3つは、その記録。</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>【論題2】気づいている「僕」と、気づいていない「私」。どちらが危ういか　―― 二つの語り手</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+    </row>
+    <row r="13" ht="140" customHeight="1">
+      <c r="A13" s="26" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="16">
+        <f>IF(A13="","0/250字",LEN(A13)&amp;"/250字")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>論題1 仮面を捨てた先に、自由はあるか／論題2 「何の問題もない」と言う語り手は何に気づいていないか／論題3 「私」が「私」であることを支えるのは何か</t>
+          <t>【論題3】二つの作品は、「私」を支えるものを示せているか　―― 二つの結末</t>
         </is>
       </c>
       <c r="B15" s="25" t="n"/>
       <c r="C15" s="25" t="n"/>
       <c r="D15" s="25" t="n"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>【300字に必ず入れること】
-① 自分の観点と、本文の根拠を示して主張したこと
-② 他の観点を受けて、考えをどう見直したか（「しかし」「とはいえ」を使う）
-③ 自分の観点では見えなかったこと（Sをねらう人）</t>
-        </is>
-      </c>
+    <row r="16" ht="140" customHeight="1">
+      <c r="A16" s="26" t="n"/>
       <c r="B16" s="26" t="n"/>
       <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>★ ①と②の両方がないとA以上にならない。</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n"/>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>【話し合いの前】私の観点／主張1文／本文の根拠2つ</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-    </row>
-    <row r="19" ht="84" customHeight="1">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>🤖 主張が書けたら【壁打ち②】へ。観点は変えず、深めるヒントをもらう。</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="24" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
+      <c r="D16" s="16">
+        <f>IF(A16="","0/250字",LEN(A16)&amp;"/250字")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>🤖 3つ書けたら【壁打ち】へ。根拠の弱いところと、出そうな反論だけもらう。観点は変えず、答えは書かせない。</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>■ 話し合いのあと（6時・7時）</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>【見直し】どの論題で、だれの、どの観点からの発言で考えが動いたか。そして今の自分の考え（200字）</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="26" t="n"/>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="29">
+        <f>IF(A21="","0/200字",LEN(A21)&amp;"/200字")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>【話し合いの後】考えが動いたところ（だれの、どの観点から）</t>
+          <t>🤖 書けたら【見直しチェック】へ。①②③のチェックだけもらう。書き直しはしてもらわない。</t>
         </is>
       </c>
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="27" t="n"/>
     </row>
-    <row r="23" ht="72" customHeight="1">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>【まとめ】ディスカッションを終えて（300字）　★提出するのはここ</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="n"/>
-      <c r="C24" s="28" t="n"/>
-      <c r="D24" s="28" t="n"/>
-    </row>
-    <row r="25" ht="180" customHeight="1">
-      <c r="A25" s="22" t="n"/>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="29">
-        <f>IF(A25="","0/300字",LEN(A25)&amp;"/300字")</f>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>■ AIの評価と自分の評価</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>AIの評価（記述だけの暫定）</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>AIのコメント</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="32" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>自分の評価（S〜D）</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="33" t="n"/>
+      <c r="D27" s="33" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>🤖 ずれた時がいちばん学べる。どちらが正しいかではなく、なぜずれたかを考える。</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>【評価のちがい】なぜずれた（一致した）のか　100字</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="n"/>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="66" customHeight="1">
+      <c r="A30" s="26" t="n"/>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="16">
+        <f>IF(A30="","0/100字",LEN(A30)&amp;"/100字")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>🤖 書けたら【見直し】へ。①②③のチェックだけもらう。書き直しはしてもらわない。</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>■ AIの評価と自分の評価</t>
-        </is>
-      </c>
-      <c r="B28" s="30" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="30" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>AIの評価</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="54" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>AIのコメント</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>自分の評価（S〜D）</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="33" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
-        <is>
-          <t>🤖 ずれた時がいちばん学べる。どちらが正しいかではなく、なぜずれたかを考える。</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="n"/>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>■ ふりかえり</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>【評価のちがい】なぜずれた（一致した）のか　100字</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-    </row>
-    <row r="34" ht="66" customHeight="1">
-      <c r="A34" s="22" t="n"/>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="23">
-        <f>IF(A34="","0/100字",LEN(A34)&amp;"/100字")</f>
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>【ふりかえり】自分の読み方はどこが変わったか　150字</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="26" t="n"/>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="16">
+        <f>IF(A34="","0/150字",LEN(A34)&amp;"/150字")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>■ ふりかえり</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t>【ふりかえり】自分の読み方はどこが変わったか　150字</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="23">
-        <f>IF(A38="","0/150字",LEN(A38)&amp;"/150字")</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="31">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="C27:D27"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2030,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
@@ -2044,7 +1838,7 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>名前は書かない／まず自分で書く／書かせるのではなく、ヒントをもらう</t>
         </is>
@@ -2053,21 +1847,31 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>【壁打ち①】発問を書いたあと（3時・4時）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="210" customHeight="1">
+          <t>【壁打ち】3つの考えを書いたあと（4時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="330" customHeight="1">
       <c r="A5" s="34" t="inlineStr">
         <is>
           <t>中学3年生にわかる言葉で答えてください。
-「素顔同盟」と「私」を、批判的に読む学習をしています。
-下は私の答えです。考えを深めるヒントを3点だけください。
-1 本文の根拠が足りないところ
-2 私が疑わずに通している前提
-3 反対の立場から出そうな反論
-書き直しはしないでください。ヒントだけ、300字以内で。
-【私の答え】
+「素顔同盟」（すやまたけし）と「私」（三崎亜記）について、3つの論題でグループ討論をします。
+論題1 仮面とデータは、同じものか
+論題2 気づいている「僕」と、気づいていない「私」。どちらが危ういか
+論題3 二つの作品は、「私」を支えるものを示せているか
+私は「批評・評価」と、自分で決めた観点から答えます。
+下が3つの論題への私の考えです。次の2点だけ教えてください。
+1 本文の根拠が弱いところ（どの論題の、どこか）
+2 班の人から出そうな反論
+★私の観点を別の観点に変える提案はしないでください。この観点のまま深めるヒントを。
+★答えを代わりに書かないでください。300字以内で。
+【私の観点】
+★ここに貼る★
+【論題1への考え】
+★ここに貼る★
+【論題2への考え】
+★ここに貼る★
+【論題3への考え】
 ★ここに貼る★</t>
         </is>
       </c>
@@ -2075,47 +1879,21 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>【壁打ち②】話し合いの前（4時）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="1">
+          <t>【見直しチェック】200字を書いたあと（7時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="200" customHeight="1">
       <c r="A8" s="34" t="inlineStr">
         <is>
           <t>中学3年生にわかる言葉で答えてください。
-「素顔同盟」と「私」について、グループで話し合います。論題はこれです。
-★論題をここに貼る★
-私はこの論題に、自分で決めた観点から答えます。
-下が私の主張と根拠です。次の2点だけ教えてください。
-1 本文の根拠として弱いところ
-2 班の人から出そうな反論
-★私の観点を別の観点に変える提案はしないでください。この観点のまま深めるヒントを。
-★主張を代わりに書かないでください。300字以内で。
-【私の観点】
-★ここに貼る★
-【主張と根拠】
-★ここに貼る★</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>【見直し】300字を書いたあと（7時）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="210" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>中学3年生にわかる言葉で答えてください。
-グループディスカッションを終えて書いた300字です。次をチェックしてください。
-□ ① 自分の観点と本文の根拠を示して主張したことが書けているか
-□ ② 他の観点を受けて考えをどう見直したかが書けているか
-□ ③ 自分の観点では見えなかったことに触れているか
-□ 話し合いの感想だけになっていないか
+グループ討論のあとに書いた200字です。次をチェックしてください。
+□ ① どの論題で、だれの、どの観点からの発言で考えが動いたかが書けているか
+□ ② 自分の観点では見えなかったことに触れているか
+□ ③ 話し合いを経た「今の自分の考え」が書けているか
+□ 「いろいろな意見が出た」だけの感想になっていないか
 書き直した文章は出さないでください。ヒントだけ、300字以内で。
-【私の300字】
+【私の200字】
 ★ここに貼る★</t>
         </is>
       </c>
@@ -2131,7 +1909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2163,7 +1941,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>必修は「批評・評価」。あと1〜2個を9つから選ぶ。（登場人物／設定／構成／視点・語り／表現の工夫／題名／主題／自分に生かす）</t>
+          <t>必修は「批評・評価」。あと1〜2個を残り8つから選ぶ。（登場人物／設定／構成／視点・語り／表現の工夫／題名／主題／自分に生かす）</t>
         </is>
       </c>
       <c r="B4" s="13" t="n"/>
@@ -2173,12 +1951,12 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>私の観点（9つから1〜2個）</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
+          <t>私の観点（批評・評価＋1〜2個）</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -2186,9 +1964,9 @@
           <t>選んだ理由</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -2196,29 +1974,29 @@
           <t>2時：その観点で「素顔同盟」から見えたこと</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
+      <c r="B7" s="26" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>4時：その観点で「私」から見えたこと</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
+          <t>3時：その観点で「私」から見えたこと</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>2時のおわりに先生が見ます。観点がばらけるように班を組みます。</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -2231,18 +2009,18 @@
       <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr"/>
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>素顔同盟</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>私</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>気づいたこと</t>
         </is>
@@ -2254,9 +2032,9 @@
           <t>★「私」を消すものは何か</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -2264,9 +2042,9 @@
           <t>★語り手はどんな立場か</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -2274,9 +2052,9 @@
           <t>★語り手は気づいているか</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
@@ -2284,9 +2062,9 @@
           <t>★引用したい一文</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -2294,9 +2072,9 @@
           <t>結末で語り手は何をするか</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -2304,302 +2082,364 @@
           <t>この作品は何を良いこととするか</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>③ 提案メモ（4時に作り、5時・6時に読む）</t>
+          <t>③ 話し合いの進め方　―― 1ラウンド10分／役割は毎回交代</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>論題は班でおなじ。あなたは自分の観点から答える。だから人とちがってよい。</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>0〜2分</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>提案者が話す（観点＋主張＋本文の根拠2つ）</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>私が提案者になる論題（1・2・3）</t>
+          <t>2〜8分</t>
         </is>
       </c>
       <c r="B22" s="10" t="n"/>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>検討。ほかの人は全員、質問か反論を1回以上</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>私の観点</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-    </row>
-    <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>主張（「◯◯の観点から見ると…」）</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>本文の根拠①（引用＋ページ・行）</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-    </row>
-    <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>本文の根拠②（引用＋ページ・行）</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-    </row>
-    <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>出そうな反論と、自分の答え</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>④ 記録係シート（5時・6時）</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+          <t>8〜10分</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>提案者が答える。到達点を1文にする</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>引用チェック係</t>
+        </is>
+      </c>
+      <c r="B24" s="35" t="n"/>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>「本文のどこ？」を必ず1回きく</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>疑い係</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="n"/>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>「しかし」「とはいえ」で始める発言を必ず1回</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>記録係</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="n"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>主張と到達点を1行ずつ書く</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>④ 当日メモ（5時・6時のはじめに書く）</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>発表する論題は当日に知らされる。「考えをまとめる」シートの該当欄を開いて、2分で話す順番を整える。</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>私が発表する論題（1・2・3）</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>話す順番（①主張 ②根拠 ③反論への答え）</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>⑤ 記録係シート（5時・6時）</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>ラウンド</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>提案者の主張</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>到達点（1文）</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>観点</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>5時 論題1</t>
-        </is>
-      </c>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>5時 論題2</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>5時 論題3</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>6時 論題1</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>6時 論題2</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
+          <t>5時 論題1</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>5時 論題2</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>5時 論題3</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>6時 論題1</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>6時 論題2</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
           <t>6時 論題3</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>⑤ 6時のおわりに　★300字の材料</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-    </row>
-    <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>⑥ 6時のおわりに　★「見直し」200字の材料</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="48" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>私の観点だから見えたこと</t>
         </is>
       </c>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-    </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="B43" s="26" t="n"/>
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="26" t="n"/>
+    </row>
+    <row r="44" ht="48" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>私の観点では見えなかったこと（だれの、どの観点から）</t>
         </is>
       </c>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-    </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="B44" s="26" t="n"/>
+      <c r="C44" s="26" t="n"/>
+      <c r="D44" s="26" t="n"/>
+    </row>
+    <row r="45" ht="48" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>自分の読みはどう変わったか</t>
         </is>
       </c>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>⑥ 7時 まとめのディスカッション　聞きながら書く</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-    </row>
-    <row r="44" ht="46" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="B45" s="26" t="n"/>
+      <c r="C45" s="26" t="n"/>
+      <c r="D45" s="26" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>⑦ 7時 まとめのディスカッション　聞きながら書く</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+    </row>
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>パネル①で考えが動いた発言（だれの、どの観点から）</t>
         </is>
       </c>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-    </row>
-    <row r="45" ht="46" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="B48" s="26" t="n"/>
+      <c r="C48" s="26" t="n"/>
+      <c r="D48" s="26" t="n"/>
+    </row>
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">　なぜ動いたのか</t>
         </is>
       </c>
-      <c r="B45" s="22" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-    </row>
-    <row r="46" ht="46" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="B49" s="26" t="n"/>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="26" t="n"/>
+    </row>
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>パネル②で考えが動いた発言</t>
         </is>
       </c>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-    </row>
-    <row r="47" ht="46" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="B50" s="26" t="n"/>
+      <c r="C50" s="26" t="n"/>
+      <c r="D50" s="26" t="n"/>
+    </row>
+    <row r="51" ht="46" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">　なぜ動いたのか</t>
         </is>
       </c>
-      <c r="B47" s="22" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
+      <c r="B51" s="26" t="n"/>
+      <c r="C51" s="26" t="n"/>
+      <c r="D51" s="26" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="B23:D23"/>
+  <mergeCells count="36">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A38:D38"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A43:D43"/>
     <mergeCell ref="B44:D44"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A28:D28"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B49:D49"/>
     <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B51:D51"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/単元_素顔同盟_私/生徒用ワークシート.xlsx
+++ b/単元_素顔同盟_私/生徒用ワークシート.xlsx
@@ -656,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -938,7 +938,7 @@
       <c r="E25" s="15" t="n"/>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>二つの作品で「私」を消しているもの</t>
+          <t>「私」を消しているもの</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>気づいている「僕」と、気づいていない「私」。どちらが危ういか</t>
+          <t>訴えた人は、救われたか</t>
         </is>
       </c>
       <c r="C26" s="15" t="n"/>
@@ -958,7 +958,7 @@
       <c r="E26" s="15" t="n"/>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>二つの語り手</t>
+          <t>仮面を外した彼女／データを消された女性</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>二つの作品は、「私」を支えるものを示せているか</t>
+          <t>この社会を続けさせているのは、誰か</t>
         </is>
       </c>
       <c r="C27" s="15" t="n"/>
@@ -978,7 +978,7 @@
       <c r="E27" s="15" t="n"/>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>二つの結末</t>
+          <t>友人（素顔同盟）／山中（私）</t>
         </is>
       </c>
     </row>
@@ -994,43 +994,39 @@
       <c r="E28" s="17" t="n"/>
       <c r="F28" s="17" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>3つとも、片方の作品だけでは答えられない。必ず両方から根拠を出すこと。</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>■ 授業の流れ（全7時間）</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>1時</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>「素顔同盟」「私」を読む／批判の目を知る／観点を仮決め</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2時</t>
+          <t>1時</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>「素顔同盟」を吟味／観点を決める／論題1の考えをまとめる</t>
+          <t>「素顔同盟」「私」を読む／批判の目を知る／観点を仮決め</t>
         </is>
       </c>
       <c r="C32" s="11" t="n"/>
@@ -1041,12 +1037,12 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3時</t>
+          <t>2時</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>「私」の語りと結末を吟味／論題2の考えをまとめる</t>
+          <t>「素顔同盟」を吟味／観点を決める／比較表の「素顔同盟」側</t>
         </is>
       </c>
       <c r="C33" s="11" t="n"/>
@@ -1057,12 +1053,12 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>4時</t>
+          <t>3時</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>二作比較表／論題3の考えをまとめる／3つを見直す</t>
+          <t>「私」を吟味／比較表の「私」側／論題1をまとめる</t>
         </is>
       </c>
       <c r="C34" s="11" t="n"/>
@@ -1073,12 +1069,12 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>5時</t>
+          <t>4時</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>話し合い1周目　★はじめに発表する人と論題が知らされる</t>
+          <t>論題2・3の主張と引用を決める（250字にするのは家庭学習）</t>
         </is>
       </c>
       <c r="C35" s="11" t="n"/>
@@ -1089,12 +1085,12 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>6時</t>
+          <t>5時</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>話し合い2周目　／　考えが動いたところを書く</t>
+          <t>話し合い1周目　★はじめに発表する人と論題が知らされる</t>
         </is>
       </c>
       <c r="C36" s="11" t="n"/>
@@ -1105,12 +1101,12 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>7時</t>
+          <t>6時</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>まとめのディスカッション／見直しを仕上げる</t>
+          <t>話し合い2周目　／　考えが動いたところを書く</t>
         </is>
       </c>
       <c r="C37" s="11" t="n"/>
@@ -1118,44 +1114,44 @@
       <c r="E37" s="11" t="n"/>
       <c r="F37" s="11" t="n"/>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>7時</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>まとめのディスカッション／見直しを仕上げる</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>■ 7時：まとめのディスカッション</t>
         </is>
       </c>
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="18" t="n"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>パネル①（12分）</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>仮面とデータは、同じものか</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="18" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>パネル②（12分）</t>
+          <t>パネル①（12分）</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>二つの作品は、「私」を支えるものを示せているか</t>
+          <t>訴えた人は、救われたか</t>
         </is>
       </c>
       <c r="D41" s="11" t="n"/>
@@ -1165,25 +1161,40 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>聞く人の仕事</t>
+          <t>パネル②（12分）</t>
         </is>
       </c>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>考えが動いた発言を1つ記録する</t>
+          <t>この社会を続けさせているのは、誰か</t>
         </is>
       </c>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="11" t="n"/>
       <c r="F42" s="11" t="n"/>
     </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>聞く人の仕事</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>考えが動いた発言を1つ記録する</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="42">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:F31"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="B18:F18"/>
@@ -1193,29 +1204,31 @@
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="A40:B40"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A6:F7"/>
+    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="C10:F10"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A39:F39"/>
     <mergeCell ref="C41:F41"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A24:F24"/>
-    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A43:B43"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C43:F43"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B36:F36"/>
@@ -1315,7 +1328,7 @@
       <c r="C7" s="19" t="n"/>
       <c r="D7" s="19" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
           <t>S</t>
@@ -1323,7 +1336,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>①②に加え、他の観点を受けて考えを見直し、自分の観点では見えなかったことに触れて今の考えを述べている</t>
+          <t>①②に加え、他の観点を受けて考えを見直し、自分の観点では見えなかったことに触れて今の考えを述べている（例：論題2を「表現の工夫」で読んで彼女が救われたと考えたが、「設定」の観点を聞いて、その後が本文に書かれていないことに気づいた）</t>
         </is>
       </c>
       <c r="C8" s="11" t="n"/>
@@ -1561,10 +1574,10 @@
       <c r="C6" s="23" t="n"/>
       <c r="D6" s="23" t="n"/>
     </row>
-    <row r="7" ht="32" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>【3つとも同じ3点を書く】① 批評・評価として、どう評価するか（主張1文）　② 自分の観点から見えたこと　③ 本文の根拠（引用）</t>
+          <t>【3つとも同じ3点を書く】① 批評・評価として、どう評価するか（主張1文）　② 自分の観点から見えたこと　③ 本文の根拠（引用）　★引用は【両方の作品】から出すこと</t>
         </is>
       </c>
       <c r="B7" s="24" t="n"/>
@@ -1574,7 +1587,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>【論題1】仮面とデータは、同じものか　―― 二つの作品で「私」を消しているもの</t>
+          <t>【論題1】仮面とデータは、同じものか　―― 「私」を消しているもの</t>
         </is>
       </c>
       <c r="B9" s="25" t="n"/>
@@ -1593,7 +1606,7 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>【論題2】気づいている「僕」と、気づいていない「私」。どちらが危ういか　―― 二つの語り手</t>
+          <t>【論題2】訴えた人は、救われたか　―― 仮面を外した彼女／データを消された女性</t>
         </is>
       </c>
       <c r="B12" s="25" t="n"/>
@@ -1612,7 +1625,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>【論題3】二つの作品は、「私」を支えるものを示せているか　―― 二つの結末</t>
+          <t>【論題3】この社会を続けさせているのは、誰か　―― 友人（素顔同盟）／山中（私）</t>
         </is>
       </c>
       <c r="B15" s="25" t="n"/>
@@ -2001,7 +2014,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>② 二作比較表（4時）　★の4つは必ず書く</t>
+          <t>② 二作比較表（2時・3時）　★の4つは必ず書く。3つの論題の材料になる</t>
         </is>
       </c>
       <c r="B11" s="9" t="n"/>
@@ -2029,7 +2042,7 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>★「私」を消すものは何か</t>
+          <t>★「私」を消すものは何か（→論題1）</t>
         </is>
       </c>
       <c r="B13" s="26" t="n"/>
@@ -2039,7 +2052,7 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>★語り手はどんな立場か</t>
+          <t>★訴えた人は誰で、どうなったか（→論題2）</t>
         </is>
       </c>
       <c r="B14" s="26" t="n"/>
@@ -2049,7 +2062,7 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>★語り手は気づいているか</t>
+          <t>★疑わない人は誰か（→論題3）</t>
         </is>
       </c>
       <c r="B15" s="26" t="n"/>
@@ -2069,7 +2082,7 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>結末で語り手は何をするか</t>
+          <t>語り手はどんな立場か</t>
         </is>
       </c>
       <c r="B17" s="26" t="n"/>
@@ -2079,7 +2092,7 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>この作品は何を良いこととするか</t>
+          <t>結末で語り手は何をするか</t>
         </is>
       </c>
       <c r="B18" s="26" t="n"/>

--- a/単元_素顔同盟_私/生徒用ワークシート.xlsx
+++ b/単元_素顔同盟_私/生徒用ワークシート.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="0&quot;組&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;番&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,11 @@
     <font>
       <color rgb="00555555"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -184,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -240,22 +245,31 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -264,7 +278,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,7 +299,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +732,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>自分で決めた観点と「批評・評価」の観点から二つの作品を批判的に読み、三つの論題について文章に表れたものの見方や考え方を捉えて、根拠を示してグループで話し合うことができる。</t>
+          <t>自分で決めた観点から二つの作品を批判的に読みながら、三つの論題について、文章に表れているものの見方や考え方について考えることができる。</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -1255,13 +1269,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1274,10 +1288,10 @@
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
     </row>
-    <row r="2" ht="38" customHeight="1">
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>目標：自分で決めた観点と「批評・評価」の観点から二つの作品を批判的に読み、三つの論題について文章に表れたものの見方や考え方を捉えて、根拠を示してグループで話し合うことができる。</t>
+          <t>単元目標：自分で決めた観点から二つの作品を批判的に読みながら、三つの論題について、文章に表れているものの見方や考え方について考えることができる。</t>
         </is>
       </c>
       <c r="B2" s="8" t="n"/>
@@ -1297,213 +1311,351 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>【思考・判断・表現】批判的に読む　／　見るもの：まとめた3つの記述　＋　当日の発言</t>
+          <t>【思考・判断・表現】　C 読むこと(1)イ</t>
         </is>
       </c>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>評価規準</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>「読むこと」において、文章を批判的に読みながら、文章に表れているものの見方や考え方について考えている。</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>見るもの：3つの論題の記述　＋　当日の発言　＋　見直し200字</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>★ AとBの分かれ目 ★　条件①（3つの論題すべてを、観点と本文の根拠でまとめた）と条件②（当日、自分の観点から根拠を示して発言した）の【両方】が必要</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>基準</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n"/>
-      <c r="D7" s="19" t="n"/>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>判断の目安</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>①②に加え、他の観点を受けて考えを見直し、自分の観点では見えなかったことに触れて今の考えを述べている（例：論題2を「表現の工夫」で読んで彼女が救われたと考えたが、「設定」の観点を聞いて、その後が本文に書かれていないことに気づいた）</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>①②の両方。3つの論題すべてを観点と本文の根拠でまとめ、当日も自分の観点から根拠を示して発言した</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>①②の一方だけ。準備はあるが発言が根拠に届かない、または発言はよいが3つそろっていない</t>
         </is>
       </c>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="11" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>準備が1〜2論題だけで本文の根拠がない、または発言していない</t>
+          <t>①②の両方。3つの論題すべてを観点と本文の根拠でまとめ、各論題で両作品に触れ、当日も自分の観点から根拠を示して発言した</t>
         </is>
       </c>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="11" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>D</t>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>準備がほとんどない</t>
+          <t>①②の一方だけ。準備はあるが発言が根拠に届かない、または発言はよいが3つそろっていない</t>
         </is>
       </c>
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="11" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>準備が1〜2論題だけで本文の根拠がない、または発言していない</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>準備がほとんどない</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>※ どの観点を選んだかでは評価しない。どの観点でも、根拠を示して吟味できていればよい。</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>※ AIの評価は「まとめた記述」だけを見た暫定。当日の発言は先生が加えて確定する。</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>【主体的に学習に取り組む態度】　／　見るもの：観点・3つの準備・話し合い</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>※ AIの評価は「記述」だけを見た暫定。当日の発言は先生が加えて確定する。</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>【主体的に学習に取り組む態度】</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>評価規準</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>積極的に文章を批判的に読み、学習課題に沿って、考えたことを互いに伝え合おうとしている。</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>見るもの：観点と選んだ理由（2時）・記録係シート・見えなかったこと（6時）・フロア記録</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>基準</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>判断の目安</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>自分で観点を決め、3つの論題すべてを準備し、他の観点を受けて読みを述べ直した</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>自分が選んだ観点で二作を読み通そうとし、他の観点からの指摘を受けて自分の読みを見直し、書き直している</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>自分で観点を決め、3つの論題を準備し、提案者をつとめ、ほかの回でも質問か反論をした</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>自分が選んだ観点で読み、話し合いに参加して自分の考えを述べている</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>観点や準備が未記入、または発言していない</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>観点が決まらない、または話し合いに参加していない</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>【観点別評価への読みかえ】　指導要録はA・B・Cの3段階</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>このシートの段階</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="n"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>観点別学習状況の評価</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>S ・ A</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>A（十分満足できる）</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>B（おおむね満足できる）</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>C ・ D</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>C（努力を要する）</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>※ 生徒への返却はS〜Dのまま。指導要録へはこの表で読みかえる。</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="32">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1537,7 +1689,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>目標：自分で決めた観点と「批評・評価」の観点から二つの作品を批判的に読み、三つの論題について文章に表れたものの見方や考え方を捉えて、根拠を示してグループで話し合うことができる。</t>
+          <t>目標：自分で決めた観点から二つの作品を批判的に読みながら、三つの論題について、文章に表れているものの見方や考え方について考えることができる。</t>
         </is>
       </c>
       <c r="B2" s="8" t="n"/>
@@ -1571,85 +1723,85 @@
         </is>
       </c>
       <c r="B6" s="10" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>【3つとも同じ3点を書く】① 批評・評価として、どう評価するか（主張1文）　② 自分の観点から見えたこと　③ 本文の根拠（引用）　★引用は【両方の作品】から出すこと</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n"/>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="24" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>【論題1】仮面とデータは、同じものか　―― 「私」を消しているもの</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n"/>
-      <c r="C9" s="25" t="n"/>
-      <c r="D9" s="25" t="n"/>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
     </row>
     <row r="10" ht="140" customHeight="1">
-      <c r="A10" s="26" t="n"/>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="26" t="n"/>
+      <c r="A10" s="29" t="n"/>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
       <c r="D10" s="16">
         <f>IF(A10="","0/250字",LEN(A10)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>【論題2】訴えた人は、救われたか　―― 仮面を外した彼女／データを消された女性</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
     </row>
     <row r="13" ht="140" customHeight="1">
-      <c r="A13" s="26" t="n"/>
-      <c r="B13" s="26" t="n"/>
-      <c r="C13" s="26" t="n"/>
+      <c r="A13" s="29" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
       <c r="D13" s="16">
         <f>IF(A13="","0/250字",LEN(A13)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>【論題3】この社会を続けさせているのは、誰か　―― 友人（素顔同盟）／山中（私）</t>
         </is>
       </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
     </row>
     <row r="16" ht="140" customHeight="1">
-      <c r="A16" s="26" t="n"/>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="26" t="n"/>
+      <c r="A16" s="29" t="n"/>
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="29" t="n"/>
       <c r="D16" s="16">
         <f>IF(A16="","0/250字",LEN(A16)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>🤖 3つ書けたら【壁打ち】へ。根拠の弱いところと、出そうな反論だけもらう。観点は変えず、答えは書かせない。</t>
         </is>
       </c>
-      <c r="B17" s="27" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="27" t="n"/>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="30" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -1662,43 +1814,43 @@
       <c r="D19" s="8" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>【見直し】どの論題で、だれの、どの観点からの発言で考えが動いたか。そして今の自分の考え（200字）</t>
         </is>
       </c>
-      <c r="B20" s="28" t="n"/>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="28" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
     </row>
     <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="26" t="n"/>
-      <c r="B21" s="26" t="n"/>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="29">
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="32">
         <f>IF(A21="","0/200字",LEN(A21)&amp;"/200字")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>🤖 書けたら【見直しチェック】へ。①②③のチェックだけもらう。書き直しはしてもらわない。</t>
         </is>
       </c>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
+      <c r="B22" s="30" t="n"/>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="30" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>■ AIの評価と自分の評価</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="30" t="n"/>
+      <c r="B24" s="33" t="n"/>
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -1707,8 +1859,8 @@
         </is>
       </c>
       <c r="B25" s="10" t="n"/>
-      <c r="C25" s="31" t="n"/>
-      <c r="D25" s="31" t="n"/>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="34" t="n"/>
     </row>
     <row r="26" ht="54" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
@@ -1717,8 +1869,8 @@
         </is>
       </c>
       <c r="B26" s="10" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -1727,33 +1879,33 @@
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="33" t="n"/>
+      <c r="C27" s="36" t="n"/>
+      <c r="D27" s="36" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>🤖 ずれた時がいちばん学べる。どちらが正しいかではなく、なぜずれたかを考える。</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
+      <c r="B28" s="30" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="30" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>【評価のちがい】なぜずれた（一致した）のか　100字</t>
         </is>
       </c>
-      <c r="B29" s="28" t="n"/>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="n"/>
+      <c r="B29" s="31" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
     </row>
     <row r="30" ht="66" customHeight="1">
-      <c r="A30" s="26" t="n"/>
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="26" t="n"/>
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="29" t="n"/>
+      <c r="C30" s="29" t="n"/>
       <c r="D30" s="16">
         <f>IF(A30="","0/100字",LEN(A30)&amp;"/100字")</f>
         <v/>
@@ -1770,19 +1922,19 @@
       <c r="D32" s="18" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>【ふりかえり】自分の読み方はどこが変わったか　150字</t>
         </is>
       </c>
-      <c r="B33" s="28" t="n"/>
-      <c r="C33" s="28" t="n"/>
-      <c r="D33" s="28" t="n"/>
+      <c r="B33" s="31" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
     </row>
     <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="26" t="n"/>
-      <c r="B34" s="26" t="n"/>
-      <c r="C34" s="26" t="n"/>
+      <c r="A34" s="29" t="n"/>
+      <c r="B34" s="29" t="n"/>
+      <c r="C34" s="29" t="n"/>
       <c r="D34" s="16">
         <f>IF(A34="","0/150字",LEN(A34)&amp;"/150字")</f>
         <v/>
@@ -1865,7 +2017,7 @@
       </c>
     </row>
     <row r="5" ht="330" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>中学3年生にわかる言葉で答えてください。
 「素顔同盟」（すやまたけし）と「私」（三崎亜記）について、3つの論題でグループ討論をします。
@@ -1897,7 +2049,7 @@
       </c>
     </row>
     <row r="8" ht="200" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>中学3年生にわかる言葉で答えてください。
 グループ討論のあとに書いた200字です。次をチェックしてください。
@@ -1967,9 +2119,9 @@
           <t>私の観点（批評・評価＋1〜2個）</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n"/>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="26" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -1977,9 +2129,9 @@
           <t>選んだ理由</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n"/>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="26" t="n"/>
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -1987,9 +2139,9 @@
           <t>2時：その観点で「素顔同盟」から見えたこと</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n"/>
-      <c r="C7" s="26" t="n"/>
-      <c r="D7" s="26" t="n"/>
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="n"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
@@ -1997,9 +2149,9 @@
           <t>3時：その観点で「私」から見えたこと</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n"/>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="26" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
@@ -2022,18 +2174,18 @@
       <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr"/>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr"/>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>素顔同盟</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>私</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>気づいたこと</t>
         </is>
@@ -2045,9 +2197,9 @@
           <t>★「私」を消すものは何か（→論題1）</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n"/>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -2055,9 +2207,9 @@
           <t>★訴えた人は誰で、どうなったか（→論題2）</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -2065,9 +2217,9 @@
           <t>★疑わない人は誰か（→論題3）</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
@@ -2075,9 +2227,9 @@
           <t>★引用したい一文</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -2085,9 +2237,9 @@
           <t>語り手はどんな立場か</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="26" t="n"/>
+      <c r="B17" s="29" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -2095,9 +2247,9 @@
           <t>結末で語り手は何をするか</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="26" t="n"/>
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -2152,12 +2304,12 @@
       <c r="D23" s="11" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>引用チェック係</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n"/>
+      <c r="B24" s="38" t="n"/>
       <c r="C24" s="11" t="inlineStr">
         <is>
           <t>「本文のどこ？」を必ず1回きく</t>
@@ -2166,12 +2318,12 @@
       <c r="D24" s="11" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>疑い係</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n"/>
+      <c r="B25" s="38" t="n"/>
       <c r="C25" s="11" t="inlineStr">
         <is>
           <t>「しかし」「とはいえ」で始める発言を必ず1回</t>
@@ -2180,12 +2332,12 @@
       <c r="D25" s="11" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="38" t="inlineStr">
         <is>
           <t>記録係</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n"/>
+      <c r="B26" s="38" t="n"/>
       <c r="C26" s="11" t="inlineStr">
         <is>
           <t>主張と到達点を1行ずつ書く</t>
@@ -2244,22 +2396,22 @@
       <c r="D33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>ラウンド</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>提案者の主張</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>到達点（1文）</t>
         </is>
       </c>
-      <c r="D34" s="19" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>観点</t>
         </is>
@@ -2271,9 +2423,9 @@
           <t>5時 論題1</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n"/>
-      <c r="C35" s="26" t="n"/>
-      <c r="D35" s="26" t="n"/>
+      <c r="B35" s="29" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="29" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -2281,9 +2433,9 @@
           <t>5時 論題2</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n"/>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="26" t="n"/>
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2291,9 +2443,9 @@
           <t>5時 論題3</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n"/>
-      <c r="C37" s="26" t="n"/>
-      <c r="D37" s="26" t="n"/>
+      <c r="B37" s="29" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -2301,9 +2453,9 @@
           <t>6時 論題1</t>
         </is>
       </c>
-      <c r="B38" s="26" t="n"/>
-      <c r="C38" s="26" t="n"/>
-      <c r="D38" s="26" t="n"/>
+      <c r="B38" s="29" t="n"/>
+      <c r="C38" s="29" t="n"/>
+      <c r="D38" s="29" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2311,9 +2463,9 @@
           <t>6時 論題2</t>
         </is>
       </c>
-      <c r="B39" s="26" t="n"/>
-      <c r="C39" s="26" t="n"/>
-      <c r="D39" s="26" t="n"/>
+      <c r="B39" s="29" t="n"/>
+      <c r="C39" s="29" t="n"/>
+      <c r="D39" s="29" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -2321,9 +2473,9 @@
           <t>6時 論題3</t>
         </is>
       </c>
-      <c r="B40" s="26" t="n"/>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="26" t="n"/>
+      <c r="B40" s="29" t="n"/>
+      <c r="C40" s="29" t="n"/>
+      <c r="D40" s="29" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
@@ -2341,9 +2493,9 @@
           <t>私の観点だから見えたこと</t>
         </is>
       </c>
-      <c r="B43" s="26" t="n"/>
-      <c r="C43" s="26" t="n"/>
-      <c r="D43" s="26" t="n"/>
+      <c r="B43" s="29" t="n"/>
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="29" t="n"/>
     </row>
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
@@ -2351,9 +2503,9 @@
           <t>私の観点では見えなかったこと（だれの、どの観点から）</t>
         </is>
       </c>
-      <c r="B44" s="26" t="n"/>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="26" t="n"/>
+      <c r="B44" s="29" t="n"/>
+      <c r="C44" s="29" t="n"/>
+      <c r="D44" s="29" t="n"/>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
@@ -2361,9 +2513,9 @@
           <t>自分の読みはどう変わったか</t>
         </is>
       </c>
-      <c r="B45" s="26" t="n"/>
-      <c r="C45" s="26" t="n"/>
-      <c r="D45" s="26" t="n"/>
+      <c r="B45" s="29" t="n"/>
+      <c r="C45" s="29" t="n"/>
+      <c r="D45" s="29" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="18" t="inlineStr">
@@ -2381,9 +2533,9 @@
           <t>パネル①で考えが動いた発言（だれの、どの観点から）</t>
         </is>
       </c>
-      <c r="B48" s="26" t="n"/>
-      <c r="C48" s="26" t="n"/>
-      <c r="D48" s="26" t="n"/>
+      <c r="B48" s="29" t="n"/>
+      <c r="C48" s="29" t="n"/>
+      <c r="D48" s="29" t="n"/>
     </row>
     <row r="49" ht="46" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
@@ -2391,9 +2543,9 @@
           <t xml:space="preserve">　なぜ動いたのか</t>
         </is>
       </c>
-      <c r="B49" s="26" t="n"/>
-      <c r="C49" s="26" t="n"/>
-      <c r="D49" s="26" t="n"/>
+      <c r="B49" s="29" t="n"/>
+      <c r="C49" s="29" t="n"/>
+      <c r="D49" s="29" t="n"/>
     </row>
     <row r="50" ht="46" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
@@ -2401,9 +2553,9 @@
           <t>パネル②で考えが動いた発言</t>
         </is>
       </c>
-      <c r="B50" s="26" t="n"/>
-      <c r="C50" s="26" t="n"/>
-      <c r="D50" s="26" t="n"/>
+      <c r="B50" s="29" t="n"/>
+      <c r="C50" s="29" t="n"/>
+      <c r="D50" s="29" t="n"/>
     </row>
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
@@ -2411,9 +2563,9 @@
           <t xml:space="preserve">　なぜ動いたのか</t>
         </is>
       </c>
-      <c r="B51" s="26" t="n"/>
-      <c r="C51" s="26" t="n"/>
-      <c r="D51" s="26" t="n"/>
+      <c r="B51" s="29" t="n"/>
+      <c r="C51" s="29" t="n"/>
+      <c r="D51" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="36">

--- a/単元_素顔同盟_私/生徒用ワークシート.xlsx
+++ b/単元_素顔同盟_私/生徒用ワークシート.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="0&quot;組&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;番&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +74,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="10"/>
     </font>
@@ -105,7 +119,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -145,6 +159,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -189,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -245,7 +269,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -257,28 +284,37 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -287,19 +323,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1269,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1301,7 +1337,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>この単元で評価するのは【思考・判断・表現】と【主体的に学習に取り組む態度】の2つ。</t>
+          <t>この単元で評価するのは【思考・判断・表現】と【主体的に学習に取り組む態度】の2つ。知識・技能は指導のみで、評価は別の単元で行う。</t>
         </is>
       </c>
       <c r="B3" s="13" t="n"/>
@@ -1309,353 +1345,461 @@
       <c r="D3" s="13" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>【思考・判断・表現】　C 読むこと(1)イ</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>【知識・技能】　(1)イ　語感を磨き語彙を豊かにする　＜本単元では評価しない＞</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>★ この単元では【指導だけ】を行い、評価はしない。第3時に「私」のカギカッコ付きの語（「解決」「誠意」「模範的」「正常な状態」）を扱う。評価は別の単元または定期テストで行う。</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>評価規準</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>「読むこと」において、文章を批判的に読みながら、文章に表れているものの見方や考え方について考えている。</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="n"/>
-      <c r="D6" s="19" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>見るもの：3つの論題の記述　＋　当日の発言　＋　見直し200字</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="n"/>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>語句の意味や働きに注意して文章を読むことを通して、語感を磨き語彙を豊かにしている。</t>
+        </is>
+      </c>
       <c r="C7" s="20" t="n"/>
       <c r="D7" s="20" t="n"/>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>見るもの：（評価する場合）カギカッコ付きの語の働きを説明した記述</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>判断の目安</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>選んだ語の働きを、語り手の立場（制度を運用する側）と結びつけて説明している。例「『解決』とは相手が満足することであって、問題が解決することではない、と語り手自身が知っている」</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>その語が「言葉だけは立派で中身が空」と示すことを説明し、自分の経験を挙げている</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>語を挙げるだけ、または経験を挙げるだけ</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>【思考・判断・表現】　C 読むこと(1)イ　＜この単元で評価する＞</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>評価規準</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>「読むこと」において、文章を批判的に読みながら、文章に表れているものの見方や考え方について考えている。</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>見るもの：3つの論題の記述　＋　当日の発言　＋　見直し200字</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>★ AとBの分かれ目 ★　条件①（3つの論題すべてを、観点と本文の根拠でまとめた）と条件②（当日、自分の観点から根拠を示して発言した）の【両方】が必要</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>判断の目安</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>①②に加え、他の観点を受けて考えを見直し、自分の観点では見えなかったことに触れて今の考えを述べている（例：論題2を「表現の工夫」で読んで彼女が救われたと考えたが、「設定」の観点を聞いて、その後が本文に書かれていないことに気づいた）</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>①②の両方。3つの論題すべてを観点と本文の根拠でまとめ、各論題で両作品に触れ、当日も自分の観点から根拠を示して発言した</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>①②の一方だけ。準備はあるが発言が根拠に届かない、または発言はよいが3つそろっていない</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>準備が1〜2論題だけで本文の根拠がない、または発言していない</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>準備がほとんどない</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>※ どの観点を選んだかでは評価しない。どの観点でも、根拠を示して吟味できていればよい。</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>※ AIの評価は「記述」だけを見た暫定。当日の発言は先生が加えて確定する。</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>【主体的に学習に取り組む態度】</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>評価規準</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>積極的に文章を批判的に読み、学習課題に沿って、考えたことを互いに伝え合おうとしている。</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>見るもの：観点と選んだ理由（2時）・記録係シート・見えなかったこと（6時）・フロア記録</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>段階</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>判断の目安</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>自分が選んだ観点で二作を読み通そうとし、他の観点からの指摘を受けて自分の読みを見直し、書き直している</t>
         </is>
       </c>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="11" t="n"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>B</t>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>自分が選んだ観点で読み、話し合いに参加して自分の考えを述べている</t>
+          <t>準備がほとんどない</t>
         </is>
       </c>
       <c r="C23" s="11" t="n"/>
       <c r="D23" s="11" t="n"/>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>※ どの観点を選んだかでは評価しない。どの観点でも、根拠を示して吟味できていればよい。</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>※ AIの評価は「記述」だけを見た暫定。当日の発言は先生が加えて確定する。</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>【主体的に学習に取り組む態度】　＜この単元で評価する＞</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>評価規準</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>積極的に文章を批判的に読み、学習課題に沿って、考えたことを互いに伝え合おうとしている。</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>見るもの：観点と選んだ理由（2時）・記録係シート・見えなかったこと（6時）・フロア記録</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>判断の目安</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>自分が選んだ観点で二作を読み通そうとし、他の観点からの指摘を受けて自分の読みを見直し、書き直している</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>自分が選んだ観点で読み、話し合いに参加して自分の考えを述べている</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>観点が決まらない、または話し合いに参加していない</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>【観点別評価への読みかえ】　指導要録はA・B・Cの3段階</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>このシートの段階</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n"/>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>観点別学習状況の評価</t>
         </is>
       </c>
-      <c r="D27" s="21" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="D36" s="22" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>S ・ A</t>
         </is>
       </c>
-      <c r="B28" s="24" t="n"/>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="B37" s="28" t="n"/>
+      <c r="C37" s="29" t="inlineStr">
         <is>
           <t>A（十分満足できる）</t>
         </is>
       </c>
-      <c r="D28" s="25" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="D37" s="29" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="29" t="inlineStr">
         <is>
           <t>B（おおむね満足できる）</t>
         </is>
       </c>
-      <c r="D29" s="25" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="D38" s="29" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>C ・ D</t>
         </is>
       </c>
-      <c r="B30" s="24" t="n"/>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="29" t="inlineStr">
         <is>
           <t>C（努力を要する）</t>
         </is>
       </c>
-      <c r="D30" s="25" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>※ 生徒への返却はS〜Dのまま。指導要録へはこの表で読みかえる。</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
+      <c r="D39" s="29" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>※ 生徒への返却はS〜Dのまま。指導要録へはこの表で読みかえる。知識・技能と態度はもともとA・B・Cなので、そのまま転記する。</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="40">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1723,85 +1867,85 @@
         </is>
       </c>
       <c r="B6" s="10" t="n"/>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="26" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="30" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>【3つとも同じ3点を書く】① 批評・評価として、どう評価するか（主張1文）　② 自分の観点から見えたこと　③ 本文の根拠（引用）　★引用は【両方の作品】から出すこと</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="31" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>【論題1】仮面とデータは、同じものか　―― 「私」を消しているもの</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n"/>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="28" t="n"/>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="32" t="n"/>
     </row>
     <row r="10" ht="140" customHeight="1">
-      <c r="A10" s="29" t="n"/>
-      <c r="B10" s="29" t="n"/>
-      <c r="C10" s="29" t="n"/>
+      <c r="A10" s="33" t="n"/>
+      <c r="B10" s="33" t="n"/>
+      <c r="C10" s="33" t="n"/>
       <c r="D10" s="16">
         <f>IF(A10="","0/250字",LEN(A10)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>【論題2】訴えた人は、救われたか　―― 仮面を外した彼女／データを消された女性</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
     </row>
     <row r="13" ht="140" customHeight="1">
-      <c r="A13" s="29" t="n"/>
-      <c r="B13" s="29" t="n"/>
-      <c r="C13" s="29" t="n"/>
+      <c r="A13" s="33" t="n"/>
+      <c r="B13" s="33" t="n"/>
+      <c r="C13" s="33" t="n"/>
       <c r="D13" s="16">
         <f>IF(A13="","0/250字",LEN(A13)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>【論題3】この社会を続けさせているのは、誰か　―― 友人（素顔同盟）／山中（私）</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
+      <c r="B15" s="32" t="n"/>
+      <c r="C15" s="32" t="n"/>
+      <c r="D15" s="32" t="n"/>
     </row>
     <row r="16" ht="140" customHeight="1">
-      <c r="A16" s="29" t="n"/>
-      <c r="B16" s="29" t="n"/>
-      <c r="C16" s="29" t="n"/>
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="33" t="n"/>
+      <c r="C16" s="33" t="n"/>
       <c r="D16" s="16">
         <f>IF(A16="","0/250字",LEN(A16)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>🤖 3つ書けたら【壁打ち】へ。根拠の弱いところと、出そうな反論だけもらう。観点は変えず、答えは書かせない。</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -1814,43 +1958,43 @@
       <c r="D19" s="8" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>【見直し】どの論題で、だれの、どの観点からの発言で考えが動いたか。そして今の自分の考え（200字）</t>
         </is>
       </c>
-      <c r="B20" s="31" t="n"/>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
     </row>
     <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="32">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="33" t="n"/>
+      <c r="C21" s="33" t="n"/>
+      <c r="D21" s="36">
         <f>IF(A21="","0/200字",LEN(A21)&amp;"/200字")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>🤖 書けたら【見直しチェック】へ。①②③のチェックだけもらう。書き直しはしてもらわない。</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n"/>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="34" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="33" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>■ AIの評価と自分の評価</t>
         </is>
       </c>
-      <c r="B24" s="33" t="n"/>
-      <c r="C24" s="33" t="n"/>
-      <c r="D24" s="33" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -1859,8 +2003,8 @@
         </is>
       </c>
       <c r="B25" s="10" t="n"/>
-      <c r="C25" s="34" t="n"/>
-      <c r="D25" s="34" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="38" t="n"/>
     </row>
     <row r="26" ht="54" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
@@ -1869,8 +2013,8 @@
         </is>
       </c>
       <c r="B26" s="10" t="n"/>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="35" t="n"/>
+      <c r="C26" s="39" t="n"/>
+      <c r="D26" s="39" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -1879,33 +2023,33 @@
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="36" t="n"/>
-      <c r="D27" s="36" t="n"/>
+      <c r="C27" s="40" t="n"/>
+      <c r="D27" s="40" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>🤖 ずれた時がいちばん学べる。どちらが正しいかではなく、なぜずれたかを考える。</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="30" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="34" t="n"/>
+      <c r="D28" s="34" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>【評価のちがい】なぜずれた（一致した）のか　100字</t>
         </is>
       </c>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
+      <c r="B29" s="35" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="35" t="n"/>
     </row>
     <row r="30" ht="66" customHeight="1">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="29" t="n"/>
-      <c r="C30" s="29" t="n"/>
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="33" t="n"/>
+      <c r="C30" s="33" t="n"/>
       <c r="D30" s="16">
         <f>IF(A30="","0/100字",LEN(A30)&amp;"/100字")</f>
         <v/>
@@ -1922,19 +2066,19 @@
       <c r="D32" s="18" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>【ふりかえり】自分の読み方はどこが変わったか　150字</t>
         </is>
       </c>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
+      <c r="B33" s="35" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="35" t="n"/>
     </row>
     <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="29" t="n"/>
-      <c r="B34" s="29" t="n"/>
-      <c r="C34" s="29" t="n"/>
+      <c r="A34" s="33" t="n"/>
+      <c r="B34" s="33" t="n"/>
+      <c r="C34" s="33" t="n"/>
       <c r="D34" s="16">
         <f>IF(A34="","0/150字",LEN(A34)&amp;"/150字")</f>
         <v/>
@@ -2017,7 +2161,7 @@
       </c>
     </row>
     <row r="5" ht="330" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>中学3年生にわかる言葉で答えてください。
 「素顔同盟」（すやまたけし）と「私」（三崎亜記）について、3つの論題でグループ討論をします。
@@ -2049,7 +2193,7 @@
       </c>
     </row>
     <row r="8" ht="200" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>中学3年生にわかる言葉で答えてください。
 グループ討論のあとに書いた200字です。次をチェックしてください。
@@ -2119,9 +2263,9 @@
           <t>私の観点（批評・評価＋1〜2個）</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n"/>
-      <c r="C5" s="29" t="n"/>
-      <c r="D5" s="29" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -2129,9 +2273,9 @@
           <t>選んだ理由</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n"/>
-      <c r="C6" s="29" t="n"/>
-      <c r="D6" s="29" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -2139,9 +2283,9 @@
           <t>2時：その観点で「素顔同盟」から見えたこと</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="29" t="n"/>
-      <c r="D7" s="29" t="n"/>
+      <c r="B7" s="33" t="n"/>
+      <c r="C7" s="33" t="n"/>
+      <c r="D7" s="33" t="n"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
@@ -2149,9 +2293,9 @@
           <t>3時：その観点で「私」から見えたこと</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
+      <c r="B8" s="33" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
@@ -2174,18 +2318,18 @@
       <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr"/>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr"/>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>素顔同盟</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>私</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>気づいたこと</t>
         </is>
@@ -2197,9 +2341,9 @@
           <t>★「私」を消すものは何か（→論題1）</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n"/>
-      <c r="C13" s="29" t="n"/>
-      <c r="D13" s="29" t="n"/>
+      <c r="B13" s="33" t="n"/>
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="33" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -2207,9 +2351,9 @@
           <t>★訴えた人は誰で、どうなったか（→論題2）</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n"/>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="29" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="33" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -2217,9 +2361,9 @@
           <t>★疑わない人は誰か（→論題3）</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n"/>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
+      <c r="B15" s="33" t="n"/>
+      <c r="C15" s="33" t="n"/>
+      <c r="D15" s="33" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
@@ -2227,9 +2371,9 @@
           <t>★引用したい一文</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n"/>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
+      <c r="B16" s="33" t="n"/>
+      <c r="C16" s="33" t="n"/>
+      <c r="D16" s="33" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -2237,9 +2381,9 @@
           <t>語り手はどんな立場か</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n"/>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="29" t="n"/>
+      <c r="B17" s="33" t="n"/>
+      <c r="C17" s="33" t="n"/>
+      <c r="D17" s="33" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -2247,9 +2391,9 @@
           <t>結末で語り手は何をするか</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n"/>
-      <c r="C18" s="29" t="n"/>
-      <c r="D18" s="29" t="n"/>
+      <c r="B18" s="33" t="n"/>
+      <c r="C18" s="33" t="n"/>
+      <c r="D18" s="33" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -2304,12 +2448,12 @@
       <c r="D23" s="11" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>引用チェック係</t>
         </is>
       </c>
-      <c r="B24" s="38" t="n"/>
+      <c r="B24" s="42" t="n"/>
       <c r="C24" s="11" t="inlineStr">
         <is>
           <t>「本文のどこ？」を必ず1回きく</t>
@@ -2318,12 +2462,12 @@
       <c r="D24" s="11" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="38" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>疑い係</t>
         </is>
       </c>
-      <c r="B25" s="38" t="n"/>
+      <c r="B25" s="42" t="n"/>
       <c r="C25" s="11" t="inlineStr">
         <is>
           <t>「しかし」「とはいえ」で始める発言を必ず1回</t>
@@ -2332,12 +2476,12 @@
       <c r="D25" s="11" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>記録係</t>
         </is>
       </c>
-      <c r="B26" s="38" t="n"/>
+      <c r="B26" s="42" t="n"/>
       <c r="C26" s="11" t="inlineStr">
         <is>
           <t>主張と到達点を1行ずつ書く</t>
@@ -2396,22 +2540,22 @@
       <c r="D33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>ラウンド</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>提案者の主張</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>到達点（1文）</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>観点</t>
         </is>
@@ -2423,9 +2567,9 @@
           <t>5時 論題1</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n"/>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="29" t="n"/>
+      <c r="B35" s="33" t="n"/>
+      <c r="C35" s="33" t="n"/>
+      <c r="D35" s="33" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -2433,9 +2577,9 @@
           <t>5時 論題2</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n"/>
-      <c r="C36" s="29" t="n"/>
-      <c r="D36" s="29" t="n"/>
+      <c r="B36" s="33" t="n"/>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2443,9 +2587,9 @@
           <t>5時 論題3</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n"/>
-      <c r="C37" s="29" t="n"/>
-      <c r="D37" s="29" t="n"/>
+      <c r="B37" s="33" t="n"/>
+      <c r="C37" s="33" t="n"/>
+      <c r="D37" s="33" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -2453,9 +2597,9 @@
           <t>6時 論題1</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n"/>
-      <c r="C38" s="29" t="n"/>
-      <c r="D38" s="29" t="n"/>
+      <c r="B38" s="33" t="n"/>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2463,9 +2607,9 @@
           <t>6時 論題2</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n"/>
-      <c r="C39" s="29" t="n"/>
-      <c r="D39" s="29" t="n"/>
+      <c r="B39" s="33" t="n"/>
+      <c r="C39" s="33" t="n"/>
+      <c r="D39" s="33" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -2473,9 +2617,9 @@
           <t>6時 論題3</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n"/>
-      <c r="C40" s="29" t="n"/>
-      <c r="D40" s="29" t="n"/>
+      <c r="B40" s="33" t="n"/>
+      <c r="C40" s="33" t="n"/>
+      <c r="D40" s="33" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
@@ -2493,9 +2637,9 @@
           <t>私の観点だから見えたこと</t>
         </is>
       </c>
-      <c r="B43" s="29" t="n"/>
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="29" t="n"/>
+      <c r="B43" s="33" t="n"/>
+      <c r="C43" s="33" t="n"/>
+      <c r="D43" s="33" t="n"/>
     </row>
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
@@ -2503,9 +2647,9 @@
           <t>私の観点では見えなかったこと（だれの、どの観点から）</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n"/>
-      <c r="C44" s="29" t="n"/>
-      <c r="D44" s="29" t="n"/>
+      <c r="B44" s="33" t="n"/>
+      <c r="C44" s="33" t="n"/>
+      <c r="D44" s="33" t="n"/>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
@@ -2513,9 +2657,9 @@
           <t>自分の読みはどう変わったか</t>
         </is>
       </c>
-      <c r="B45" s="29" t="n"/>
-      <c r="C45" s="29" t="n"/>
-      <c r="D45" s="29" t="n"/>
+      <c r="B45" s="33" t="n"/>
+      <c r="C45" s="33" t="n"/>
+      <c r="D45" s="33" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="18" t="inlineStr">
@@ -2533,9 +2677,9 @@
           <t>パネル①で考えが動いた発言（だれの、どの観点から）</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
-      <c r="C48" s="29" t="n"/>
-      <c r="D48" s="29" t="n"/>
+      <c r="B48" s="33" t="n"/>
+      <c r="C48" s="33" t="n"/>
+      <c r="D48" s="33" t="n"/>
     </row>
     <row r="49" ht="46" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
@@ -2543,9 +2687,9 @@
           <t xml:space="preserve">　なぜ動いたのか</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n"/>
-      <c r="C49" s="29" t="n"/>
-      <c r="D49" s="29" t="n"/>
+      <c r="B49" s="33" t="n"/>
+      <c r="C49" s="33" t="n"/>
+      <c r="D49" s="33" t="n"/>
     </row>
     <row r="50" ht="46" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
@@ -2553,9 +2697,9 @@
           <t>パネル②で考えが動いた発言</t>
         </is>
       </c>
-      <c r="B50" s="29" t="n"/>
-      <c r="C50" s="29" t="n"/>
-      <c r="D50" s="29" t="n"/>
+      <c r="B50" s="33" t="n"/>
+      <c r="C50" s="33" t="n"/>
+      <c r="D50" s="33" t="n"/>
     </row>
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
@@ -2563,9 +2707,9 @@
           <t xml:space="preserve">　なぜ動いたのか</t>
         </is>
       </c>
-      <c r="B51" s="29" t="n"/>
-      <c r="C51" s="29" t="n"/>
-      <c r="D51" s="29" t="n"/>
+      <c r="B51" s="33" t="n"/>
+      <c r="C51" s="33" t="n"/>
+      <c r="D51" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="36">

--- a/単元_素顔同盟_私/生徒用ワークシート.xlsx
+++ b/単元_素顔同盟_私/生徒用ワークシート.xlsx
@@ -11,7 +11,6 @@
     <sheet name="評価基準" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="考えをまとめる" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="AIプロンプト" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="話し合いワーク" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -119,7 +118,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -181,11 +180,6 @@
         <fgColor rgb="00EBF5FB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8DAEF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -213,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -266,6 +260,9 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -275,21 +272,21 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -303,7 +300,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -311,35 +311,17 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -706,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -744,7 +726,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>※ 組・番は半角数字</t>
+          <t>※ 組・番は半角数字　／　書きこむのは「考えをまとめる」シート1枚だけ</t>
         </is>
       </c>
       <c r="B3" s="6" t="n"/>
@@ -1156,7 +1138,7 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>話し合い2周目　／　考えが動いたところを書く</t>
+          <t>話し合い2周目　／　聞いて考えたことを書く</t>
         </is>
       </c>
       <c r="C37" s="11" t="n"/>
@@ -1172,7 +1154,7 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>まとめのディスカッション／見直しを仕上げる</t>
+          <t>まとめのディスカッション／聞いて考えたことを仕上げる</t>
         </is>
       </c>
       <c r="C38" s="11" t="n"/>
@@ -1181,27 +1163,27 @@
       <c r="F38" s="11" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>■ 7時：まとめのディスカッション</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="18" t="n"/>
-      <c r="D40" s="18" t="n"/>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="18" t="n"/>
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>■ 1ラウンド10分の中身　／　役割は毎回交代</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>パネル①（12分）</t>
+          <t>0〜2分</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>訴えた人は、救われたか</t>
+          <t>提案者が話す（観点＋主張＋本文の根拠2つ）</t>
         </is>
       </c>
       <c r="D41" s="11" t="n"/>
@@ -1211,13 +1193,13 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>パネル②（12分）</t>
+          <t>2〜8分</t>
         </is>
       </c>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>この社会を続けさせているのは、誰か</t>
+          <t>検討。ほかの人は全員、質問か反論を1回以上</t>
         </is>
       </c>
       <c r="D42" s="11" t="n"/>
@@ -1227,38 +1209,153 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>聞く人の仕事</t>
+          <t>8〜10分</t>
         </is>
       </c>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>考えが動いた発言を1つ記録する</t>
+          <t>提案者が答える。到達点を1文にする</t>
         </is>
       </c>
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="11" t="n"/>
     </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>引用チェック係</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>「本文のどこ？」を必ず1回きく</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>疑い係</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>「しかし」「とはいえ」で始める発言を必ず1回</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>記録係</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>主張と到達点を1行ずつ書く</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>■ 7時：まとめのディスカッション</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="n"/>
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>パネル①（12分）</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>訴えた人は、救われたか</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>パネル②（12分）</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>この社会を続けさせているのは、誰か</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>聞く人の仕事</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>考えが動いた発言を「考えをまとめる」シート④に書く</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="55">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="C49:F49"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="B27:E27"/>
+    <mergeCell ref="C45:F45"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A6:F7"/>
     <mergeCell ref="B38:F38"/>
@@ -1269,9 +1366,12 @@
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C41:F41"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="C44:F44"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="B33:F33"/>
@@ -1279,10 +1379,13 @@
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C43:F43"/>
+    <mergeCell ref="C46:F46"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B32:F32"/>
+    <mergeCell ref="C51:F51"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
   <dataValidations count="2">
@@ -1305,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1345,14 +1448,14 @@
       <c r="D3" s="13" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>【知識・技能】　(1)イ　語感を磨き語彙を豊かにする　＜本単元では評価しない＞</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
@@ -1370,436 +1473,425 @@
           <t>評価規準</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>語句の意味や働きに注意して文章を読むことを通して、語感を磨き語彙を豊かにしている。</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>見るもの：（評価する場合）カギカッコ付きの語の働きを説明した記述</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>判断の目安</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>選んだ語の働きを、語り手の立場（制度を運用する側）と結びつけて説明している。例「『解決』とは相手が満足することであって、問題が解決することではない、と語り手自身が知っている」</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>選んだ語の働きを、語り手の立場（制度を運用する側）と結びつけて説明している。例「『解決』とは相手が満足することであって、問題が解決することではない、と語り手自身が知っている」</t>
+          <t>その語が「言葉だけは立派で中身が空」と示すことを説明し、自分の経験を挙げている</t>
         </is>
       </c>
       <c r="C10" s="24" t="n"/>
       <c r="D10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>その語が「言葉だけは立派で中身が空」と示すことを説明し、自分の経験を挙げている</t>
+          <t>語を挙げるだけ、または経験を挙げるだけ</t>
         </is>
       </c>
       <c r="C11" s="24" t="n"/>
       <c r="D11" s="24" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>語を挙げるだけ、または経験を挙げるだけ</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>【思考・判断・表現】　C 読むこと(1)イ　＜この単元で評価する＞</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>評価規準</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>「読むこと」において、文章を批判的に読みながら、文章に表れているものの見方や考え方について考えている。</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>見るもの：3つの論題の記述　＋　当日の発言　＋　見直し200字</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="21" t="n"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>見るもの：3つの論題の記述　＋　当日の発言　＋　聞いて考えたこと（3論題分）</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>★ AとBの分かれ目 ★　条件①（3つの論題すべてを、観点と本文の根拠でまとめた）と条件②（当日、自分の観点から根拠を示して発言した）の【両方】が必要</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>判断の目安</t>
         </is>
       </c>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>①②に加え、3論題とも「聞いて考えたこと」を書き、自分の観点では見えなかったことに触れて今の考えを述べている</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>①②に加え、他の観点を受けて考えを見直し、自分の観点では見えなかったことに触れて今の考えを述べている（例：論題2を「表現の工夫」で読んで彼女が救われたと考えたが、「設定」の観点を聞いて、その後が本文に書かれていないことに気づいた）</t>
+          <t>①②の両方。3つの論題すべてを観点と本文の根拠でまとめ、各論題で両作品に触れ、当日も自分の観点から根拠を示して発言した</t>
         </is>
       </c>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="11" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>A</t>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>①②の両方。3つの論題すべてを観点と本文の根拠でまとめ、各論題で両作品に触れ、当日も自分の観点から根拠を示して発言した</t>
+          <t>①②の一方だけ。準備はあるが発言が根拠に届かない、または発言はよいが3つそろっていない</t>
         </is>
       </c>
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="11" t="n"/>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>B</t>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>①②の一方だけ。準備はあるが発言が根拠に届かない、または発言はよいが3つそろっていない</t>
+          <t>準備が1〜2論題だけで本文の根拠がない、または発言していない</t>
         </is>
       </c>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="11" t="n"/>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>C</t>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>準備が1〜2論題だけで本文の根拠がない、または発言していない</t>
+          <t>準備がほとんどない</t>
         </is>
       </c>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="11" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>準備がほとんどない</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>※ どの観点を選んだかでは評価しない。どの観点でも、根拠を示して吟味できていればよい。</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>※ AIの評価は「記述」だけを見た暫定。当日の発言は先生が加えて確定する。</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n"/>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="21" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="26" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>【主体的に学習に取り組む態度】　＜この単元で評価する＞</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>評価規準</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>積極的に文章を批判的に読み、学習課題に沿って、考えたことを互いに伝え合おうとしている。</t>
         </is>
       </c>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="25" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>見るもの：観点と選んだ理由（2時）・記録係シート・見えなかったこと（6時）・フロア記録</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="n"/>
-      <c r="C29" s="21" t="n"/>
-      <c r="D29" s="21" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>見るもの：観点と選んだ理由・記録係シート・聞いて考えたこと・ふりかえり</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>判断の目安</t>
         </is>
       </c>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>自分が選んだ観点で二作を読み通そうとし、他の観点からの指摘を受けて自分の読みを見直し、書き直している</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>自分が選んだ観点で二作を読み通そうとし、他の観点からの指摘を受けて自分の読みを見直し、書き直している</t>
+          <t>自分が選んだ観点で読み、話し合いに参加して自分の考えを述べている</t>
         </is>
       </c>
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="11" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>自分が選んだ観点で読み、話し合いに参加して自分の考えを述べている</t>
+          <t>観点が決まらない、または話し合いに参加していない</t>
         </is>
       </c>
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>観点が決まらない、または話し合いに参加していない</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>【観点別評価への読みかえ】　指導要録はA・B・Cの3段階</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>このシートの段階</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>観点別学習状況の評価</t>
         </is>
       </c>
-      <c r="D36" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>S ・ A</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>A（十分満足できる）</t>
+        </is>
+      </c>
+      <c r="D36" s="30" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>S ・ A</t>
-        </is>
-      </c>
-      <c r="B37" s="28" t="n"/>
-      <c r="C37" s="29" t="inlineStr">
-        <is>
-          <t>A（十分満足できる）</t>
-        </is>
-      </c>
-      <c r="D37" s="29" t="n"/>
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="n"/>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>B（おおむね満足できる）</t>
+        </is>
+      </c>
+      <c r="D37" s="30" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B38" s="28" t="n"/>
-      <c r="C38" s="29" t="inlineStr">
-        <is>
-          <t>B（おおむね満足できる）</t>
-        </is>
-      </c>
-      <c r="D38" s="29" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="28" t="inlineStr">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>C ・ D</t>
         </is>
       </c>
-      <c r="B39" s="28" t="n"/>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="B38" s="29" t="n"/>
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>C（努力を要する）</t>
         </is>
       </c>
-      <c r="D39" s="29" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="D38" s="30" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>※ 生徒への返却はS〜Dのまま。指導要録へはこの表で読みかえる。知識・技能と態度はもともとA・B・Cなので、そのまま転記する。</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n"/>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="21" t="n"/>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="39">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="A40:D40"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B15:D15"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1811,7 +1903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1823,14 +1915,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>考えをまとめる</t>
+          <t>考えをまとめる　―― 書きこむのはこのシートだけ</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
     </row>
-    <row r="2" ht="38" customHeight="1">
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>目標：自分で決めた観点から二つの作品を批判的に読みながら、三つの論題について、文章に表れているものの見方や考え方について考えることができる。</t>
@@ -1841,288 +1933,516 @@
       <c r="D2" s="8" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>■ 3つの論題について、考えをまとめる（2時〜4時）</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>★ 当日、どの論題で発表するか知らされる。だから3つすべて準備しておく。</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>① 自分の観点を決める（1時のおわり〜2時）</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>必修は「批評・評価」。あと1〜2個を残り8つから選ぶ。（登場人物／設定／構成／視点・語り／表現の工夫／題名／主題／自分に生かす）</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>私の観点：批評・評価（必修）＋</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>【3つとも同じ3点を書く】① 批評・評価として、どう評価するか（主張1文）　② 自分の観点から見えたこと　③ 本文の根拠（引用）　★引用は【両方の作品】から出すこと</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>【論題1】仮面とデータは、同じものか　―― 「私」を消しているもの</t>
+          <t>私の観点（批評・評価＋1〜2個）</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="31" t="n"/>
+      <c r="D6" s="31" t="n"/>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>選んだ理由</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2時：その観点で「素顔同盟」から見えたこと</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="32" t="n"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>3時：その観点で「私」から見えたこと</t>
         </is>
       </c>
       <c r="B9" s="32" t="n"/>
       <c r="C9" s="32" t="n"/>
       <c r="D9" s="32" t="n"/>
     </row>
-    <row r="10" ht="140" customHeight="1">
-      <c r="A10" s="33" t="n"/>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="16">
-        <f>IF(A10="","0/250字",LEN(A10)&amp;"/250字")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>【論題2】訴えた人は、救われたか　―― 仮面を外した彼女／データを消された女性</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="n"/>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
-    </row>
-    <row r="13" ht="140" customHeight="1">
-      <c r="A13" s="33" t="n"/>
-      <c r="B13" s="33" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="16">
-        <f>IF(A13="","0/250字",LEN(A13)&amp;"/250字")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>【論題3】この社会を続けさせているのは、誰か　―― 友人（素顔同盟）／山中（私）</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>2時のおわりに先生が見ます。観点がばらけるように班を組みます。</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>② 二作比較表（2時・3時）　★の4つは必ず書く。3つの論題の材料になる</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr"/>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>素顔同盟</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>私</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>気づいたこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>★「私」を消すものは何か（→論題1）</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="32" t="n"/>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>★訴えた人は誰で、どうなったか（→論題2）</t>
         </is>
       </c>
       <c r="B15" s="32" t="n"/>
       <c r="C15" s="32" t="n"/>
       <c r="D15" s="32" t="n"/>
     </row>
-    <row r="16" ht="140" customHeight="1">
-      <c r="A16" s="33" t="n"/>
-      <c r="B16" s="33" t="n"/>
-      <c r="C16" s="33" t="n"/>
-      <c r="D16" s="16">
-        <f>IF(A16="","0/250字",LEN(A16)&amp;"/250字")</f>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>★疑わない人は誰か（→論題3）</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>★引用したい一文</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="32" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>語り手はどんな立場か</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>結末で語り手は何をするか</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>③ 3つの論題について、考えをまとめる（3時・4時）</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>★ 当日、どの論題で発表するか知らされる。だから3つすべて準備しておく。</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>【3つとも同じ3点を書く】① 批評・評価として、どう評価するか（主張1文）　② 自分の観点から見えたこと　③ 本文の根拠（引用）　★引用は【両方の作品】から</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="n"/>
+      <c r="C23" s="33" t="n"/>
+      <c r="D23" s="33" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>【論題1】仮面とデータは、同じものか　―― 「私」を消しているもの</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="34" t="n"/>
+      <c r="D24" s="34" t="n"/>
+    </row>
+    <row r="25" ht="140" customHeight="1">
+      <c r="A25" s="32" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="16">
+        <f>IF(A25="","0/250字",LEN(A25)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>🤖 3つ書けたら【壁打ち】へ。根拠の弱いところと、出そうな反論だけもらう。観点は変えず、答えは書かせない。</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="n"/>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="34" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>■ 話し合いのあと（6時・7時）</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t>【見直し】どの論題で、だれの、どの観点からの発言で考えが動いたか。そして今の自分の考え（200字）</t>
-        </is>
-      </c>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-    </row>
-    <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="33" t="n"/>
-      <c r="B21" s="33" t="n"/>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="36">
-        <f>IF(A21="","0/200字",LEN(A21)&amp;"/200字")</f>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t>【論題2】訴えた人は、救われたか　―― 仮面を外した彼女／データを消された女性</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="34" t="n"/>
+      <c r="D26" s="34" t="n"/>
+    </row>
+    <row r="27" ht="140" customHeight="1">
+      <c r="A27" s="32" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="16">
+        <f>IF(A27="","0/250字",LEN(A27)&amp;"/250字")</f>
         <v/>
       </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="34" t="inlineStr">
-        <is>
-          <t>🤖 書けたら【見直しチェック】へ。①②③のチェックだけもらう。書き直しはしてもらわない。</t>
-        </is>
-      </c>
-      <c r="B22" s="34" t="n"/>
-      <c r="C22" s="34" t="n"/>
-      <c r="D22" s="34" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>■ AIの評価と自分の評価</t>
-        </is>
-      </c>
-      <c r="B24" s="37" t="n"/>
-      <c r="C24" s="37" t="n"/>
-      <c r="D24" s="37" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>AIの評価（記述だけの暫定）</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="38" t="n"/>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>AIのコメント</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="39" t="n"/>
-      <c r="D26" s="39" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>自分の評価（S〜D）</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="40" t="n"/>
-      <c r="D27" s="40" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="34" t="inlineStr">
         <is>
-          <t>🤖 ずれた時がいちばん学べる。どちらが正しいかではなく、なぜずれたかを考える。</t>
+          <t>【論題3】この社会を続けさせているのは、誰か　―― 友人（素顔同盟）／山中（私）</t>
         </is>
       </c>
       <c r="B28" s="34" t="n"/>
       <c r="C28" s="34" t="n"/>
       <c r="D28" s="34" t="n"/>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="35" t="inlineStr">
-        <is>
-          <t>【評価のちがい】なぜずれた（一致した）のか　100字</t>
-        </is>
-      </c>
-      <c r="B29" s="35" t="n"/>
-      <c r="C29" s="35" t="n"/>
-      <c r="D29" s="35" t="n"/>
-    </row>
-    <row r="30" ht="66" customHeight="1">
-      <c r="A30" s="33" t="n"/>
-      <c r="B30" s="33" t="n"/>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="16">
-        <f>IF(A30="","0/100字",LEN(A30)&amp;"/100字")</f>
+    <row r="29" ht="140" customHeight="1">
+      <c r="A29" s="32" t="n"/>
+      <c r="B29" s="32" t="n"/>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="16">
+        <f>IF(A29="","0/250字",LEN(A29)&amp;"/250字")</f>
         <v/>
       </c>
     </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t>🤖 3つ書けたら【壁打ち】へ。根拠の弱いところと、出そうな反論だけもらう。観点は変えず、答えは書かせない。</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="35" t="n"/>
+    </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>■ ふりかえり</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="35" t="inlineStr">
-        <is>
-          <t>【ふりかえり】自分の読み方はどこが変わったか　150字</t>
-        </is>
-      </c>
-      <c r="B33" s="35" t="n"/>
-      <c r="C33" s="35" t="n"/>
-      <c r="D33" s="35" t="n"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="33" t="n"/>
-      <c r="B34" s="33" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="16">
-        <f>IF(A34="","0/150字",LEN(A34)&amp;"/150字")</f>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>④ ディスカッションを聞いて考えたこと（5時〜7時）　★3つとも書く</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>自分の観点以外の観点からの発言を受けて、考えたことを書く。だれの、どの観点からの発言かを必ず入れること。7時のパネルで聞いたことも足す。</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="13" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>【論題1】仮面とデータは、同じものか　―― ほかの観点を受けて考えたこと</t>
+        </is>
+      </c>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="34" t="n"/>
+      <c r="D34" s="34" t="n"/>
+    </row>
+    <row r="35" ht="110" customHeight="1">
+      <c r="A35" s="32" t="n"/>
+      <c r="B35" s="32" t="n"/>
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="16">
+        <f>IF(A35="","0/200字",LEN(A35)&amp;"/200字")</f>
         <v/>
       </c>
     </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>【論題2】訴えた人は、救われたか　―― ほかの観点を受けて考えたこと</t>
+        </is>
+      </c>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n"/>
+    </row>
+    <row r="37" ht="110" customHeight="1">
+      <c r="A37" s="32" t="n"/>
+      <c r="B37" s="32" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="16">
+        <f>IF(A37="","0/200字",LEN(A37)&amp;"/200字")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="34" t="inlineStr">
+        <is>
+          <t>【論題3】この社会を続けさせているのは、誰か　―― ほかの観点を受けて考えたこと</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="34" t="n"/>
+      <c r="D38" s="34" t="n"/>
+    </row>
+    <row r="39" ht="110" customHeight="1">
+      <c r="A39" s="32" t="n"/>
+      <c r="B39" s="32" t="n"/>
+      <c r="C39" s="32" t="n"/>
+      <c r="D39" s="16">
+        <f>IF(A39="","0/200字",LEN(A39)&amp;"/200字")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>🤖 3つ書けたら【見直しチェック】へ。3点のチェックだけもらう。書き直しはしてもらわない。</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="n"/>
+      <c r="C40" s="35" t="n"/>
+      <c r="D40" s="35" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>⑤ 当日メモと記録係シート（5時・6時）</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>私が発表する論題（当日に知らされる）</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>ラウンド</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>提案者の主張</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>到達点（1文）</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>5時 論題1</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="n"/>
+      <c r="C45" s="32" t="n"/>
+      <c r="D45" s="32" t="n"/>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>5時 論題2</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="n"/>
+      <c r="C46" s="32" t="n"/>
+      <c r="D46" s="32" t="n"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>5時 論題3</t>
+        </is>
+      </c>
+      <c r="B47" s="32" t="n"/>
+      <c r="C47" s="32" t="n"/>
+      <c r="D47" s="32" t="n"/>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>6時 論題1</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="n"/>
+      <c r="C48" s="32" t="n"/>
+      <c r="D48" s="32" t="n"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>6時 論題2</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="n"/>
+      <c r="C49" s="32" t="n"/>
+      <c r="D49" s="32" t="n"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>6時 論題3</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="n"/>
+      <c r="C50" s="32" t="n"/>
+      <c r="D50" s="32" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>⑥ ふりかえり（7時）</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="n"/>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>この単元で、自分の読み方はどこが変わったか　150字</t>
+        </is>
+      </c>
+      <c r="B53" s="37" t="n"/>
+      <c r="C53" s="37" t="n"/>
+      <c r="D53" s="37" t="n"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="32" t="n"/>
+      <c r="B54" s="32" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="16">
+        <f>IF(A54="","0/150字",LEN(A54)&amp;"/150字")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="35">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A43:B43"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A54:C54"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"S,A,B,C,D"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2161,13 +2481,13 @@
       </c>
     </row>
     <row r="5" ht="330" customHeight="1">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>中学3年生にわかる言葉で答えてください。
 「素顔同盟」（すやまたけし）と「私」（三崎亜記）について、3つの論題でグループ討論をします。
 論題1 仮面とデータは、同じものか
-論題2 気づいている「僕」と、気づいていない「私」。どちらが危ういか
-論題3 二つの作品は、「私」を支えるものを示せているか
+論題2 訴えた人は、救われたか
+論題3 この社会を続けさせているのは、誰か
 私は「批評・評価」と、自分で決めた観点から答えます。
 下が3つの論題への私の考えです。次の2点だけ教えてください。
 1 本文の根拠が弱いところ（どの論題の、どこか）
@@ -2188,21 +2508,28 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>【見直しチェック】200字を書いたあと（7時）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="200" customHeight="1">
-      <c r="A8" s="41" t="inlineStr">
+          <t>【見直しチェック】聞いて考えたことを書いたあと（7時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="300" customHeight="1">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>中学3年生にわかる言葉で答えてください。
-グループ討論のあとに書いた200字です。次をチェックしてください。
-□ ① どの論題で、だれの、どの観点からの発言で考えが動いたかが書けているか
-□ ② 自分の観点では見えなかったことに触れているか
-□ ③ 話し合いを経た「今の自分の考え」が書けているか
+グループ討論を聞いて考えたことを、3つの論題それぞれについて書きました。
+次をチェックしてください。
+□ ① だれの、どの観点からの発言かが書けているか（3つとも）
+□ ② それが【自分の観点とはちがう観点】からの発言になっているか
+□ ③ その発言を受けて、自分の考えがどう動いたかが書けているか
 □ 「いろいろな意見が出た」だけの感想になっていないか
 書き直した文章は出さないでください。ヒントだけ、300字以内で。
-【私の200字】
+【私の観点】
+★ここに貼る★
+【論題1：聞いて考えたこと】
+★ここに貼る★
+【論題2：聞いて考えたこと】
+★ここに貼る★
+【論題3：聞いて考えたこと】
 ★ここに貼る★</t>
         </is>
       </c>
@@ -2210,546 +2537,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>話し合いワーク（1時〜7時）</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>① 自分の観点を決める（1時のおわり〜2時）</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="n"/>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>必修は「批評・評価」。あと1〜2個を残り8つから選ぶ。（登場人物／設定／構成／視点・語り／表現の工夫／題名／主題／自分に生かす）</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>私の観点（批評・評価＋1〜2個）</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n"/>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>選んだ理由</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
-    </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2時：その観点で「素顔同盟」から見えたこと</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-    </row>
-    <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>3時：その観点で「私」から見えたこと</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>2時のおわりに先生が見ます。観点がばらけるように班を組みます。</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>② 二作比較表（2時・3時）　★の4つは必ず書く。3つの論題の材料になる</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="inlineStr"/>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>素顔同盟</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>私</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>気づいたこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>★「私」を消すものは何か（→論題1）</t>
-        </is>
-      </c>
-      <c r="B13" s="33" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="33" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>★訴えた人は誰で、どうなったか（→論題2）</t>
-        </is>
-      </c>
-      <c r="B14" s="33" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="33" t="n"/>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>★疑わない人は誰か（→論題3）</t>
-        </is>
-      </c>
-      <c r="B15" s="33" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="33" t="n"/>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>★引用したい一文</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="n"/>
-      <c r="C16" s="33" t="n"/>
-      <c r="D16" s="33" t="n"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>語り手はどんな立場か</t>
-        </is>
-      </c>
-      <c r="B17" s="33" t="n"/>
-      <c r="C17" s="33" t="n"/>
-      <c r="D17" s="33" t="n"/>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>結末で語り手は何をするか</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="n"/>
-      <c r="C18" s="33" t="n"/>
-      <c r="D18" s="33" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>③ 話し合いの進め方　―― 1ラウンド10分／役割は毎回交代</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>0〜2分</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>提案者が話す（観点＋主張＋本文の根拠2つ）</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>2〜8分</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>検討。ほかの人は全員、質問か反論を1回以上</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>8〜10分</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>提案者が答える。到達点を1文にする</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
-        <is>
-          <t>引用チェック係</t>
-        </is>
-      </c>
-      <c r="B24" s="42" t="n"/>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>「本文のどこ？」を必ず1回きく</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>疑い係</t>
-        </is>
-      </c>
-      <c r="B25" s="42" t="n"/>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>「しかし」「とはいえ」で始める発言を必ず1回</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="42" t="inlineStr">
-        <is>
-          <t>記録係</t>
-        </is>
-      </c>
-      <c r="B26" s="42" t="n"/>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>主張と到達点を1行ずつ書く</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>④ 当日メモ（5時・6時のはじめに書く）</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>発表する論題は当日に知らされる。「考えをまとめる」シートの該当欄を開いて、2分で話す順番を整える。</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-    </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>私が発表する論題（1・2・3）</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>話す順番（①主張 ②根拠 ③反論への答え）</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>⑤ 記録係シート（5時・6時）</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>ラウンド</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>提案者の主張</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="inlineStr">
-        <is>
-          <t>到達点（1文）</t>
-        </is>
-      </c>
-      <c r="D34" s="22" t="inlineStr">
-        <is>
-          <t>観点</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>5時 論題1</t>
-        </is>
-      </c>
-      <c r="B35" s="33" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="33" t="n"/>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>5時 論題2</t>
-        </is>
-      </c>
-      <c r="B36" s="33" t="n"/>
-      <c r="C36" s="33" t="n"/>
-      <c r="D36" s="33" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>5時 論題3</t>
-        </is>
-      </c>
-      <c r="B37" s="33" t="n"/>
-      <c r="C37" s="33" t="n"/>
-      <c r="D37" s="33" t="n"/>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>6時 論題1</t>
-        </is>
-      </c>
-      <c r="B38" s="33" t="n"/>
-      <c r="C38" s="33" t="n"/>
-      <c r="D38" s="33" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>6時 論題2</t>
-        </is>
-      </c>
-      <c r="B39" s="33" t="n"/>
-      <c r="C39" s="33" t="n"/>
-      <c r="D39" s="33" t="n"/>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>6時 論題3</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="n"/>
-      <c r="C40" s="33" t="n"/>
-      <c r="D40" s="33" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>⑥ 6時のおわりに　★「見直し」200字の材料</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-    </row>
-    <row r="43" ht="48" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>私の観点だから見えたこと</t>
-        </is>
-      </c>
-      <c r="B43" s="33" t="n"/>
-      <c r="C43" s="33" t="n"/>
-      <c r="D43" s="33" t="n"/>
-    </row>
-    <row r="44" ht="48" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>私の観点では見えなかったこと（だれの、どの観点から）</t>
-        </is>
-      </c>
-      <c r="B44" s="33" t="n"/>
-      <c r="C44" s="33" t="n"/>
-      <c r="D44" s="33" t="n"/>
-    </row>
-    <row r="45" ht="48" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>自分の読みはどう変わったか</t>
-        </is>
-      </c>
-      <c r="B45" s="33" t="n"/>
-      <c r="C45" s="33" t="n"/>
-      <c r="D45" s="33" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
-        <is>
-          <t>⑦ 7時 まとめのディスカッション　聞きながら書く</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="n"/>
-      <c r="C47" s="18" t="n"/>
-      <c r="D47" s="18" t="n"/>
-    </row>
-    <row r="48" ht="46" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>パネル①で考えが動いた発言（だれの、どの観点から）</t>
-        </is>
-      </c>
-      <c r="B48" s="33" t="n"/>
-      <c r="C48" s="33" t="n"/>
-      <c r="D48" s="33" t="n"/>
-    </row>
-    <row r="49" ht="46" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　なぜ動いたのか</t>
-        </is>
-      </c>
-      <c r="B49" s="33" t="n"/>
-      <c r="C49" s="33" t="n"/>
-      <c r="D49" s="33" t="n"/>
-    </row>
-    <row r="50" ht="46" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>パネル②で考えが動いた発言</t>
-        </is>
-      </c>
-      <c r="B50" s="33" t="n"/>
-      <c r="C50" s="33" t="n"/>
-      <c r="D50" s="33" t="n"/>
-    </row>
-    <row r="51" ht="46" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　なぜ動いたのか</t>
-        </is>
-      </c>
-      <c r="B51" s="33" t="n"/>
-      <c r="C51" s="33" t="n"/>
-      <c r="D51" s="33" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="B48:D48"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>